--- a/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="162">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -23,51 +23,63 @@
     <t>heap_4.o</t>
   </si>
   <si>
+    <t>motor_loop.o</t>
+  </si>
+  <si>
     <t>startup_stm32g474xx.o</t>
   </si>
   <si>
     <t>runtime_param.o</t>
   </si>
   <si>
+    <t>c_w.l</t>
+  </si>
+  <si>
+    <t>pid_profile.o</t>
+  </si>
+  <si>
+    <t>usart.o</t>
+  </si>
+  <si>
+    <t>tasks.o</t>
+  </si>
+  <si>
+    <t>stdio_streams.o</t>
+  </si>
+  <si>
+    <t>tim.o</t>
+  </si>
+  <si>
+    <t>drv_rtos.o</t>
+  </si>
+  <si>
+    <t>spi.o</t>
+  </si>
+  <si>
+    <t>dev_dwt_counter.o</t>
+  </si>
+  <si>
     <t>adc.o</t>
   </si>
   <si>
-    <t>tasks.o</t>
-  </si>
-  <si>
-    <t>drv_rtos.o</t>
-  </si>
-  <si>
-    <t>spi.o</t>
-  </si>
-  <si>
-    <t>usart.o</t>
-  </si>
-  <si>
     <t>fdcan.o</t>
   </si>
   <si>
-    <t>c_w.l</t>
-  </si>
-  <si>
     <t>libspace.o</t>
   </si>
   <si>
-    <t>dev_dwt_counter.o</t>
-  </si>
-  <si>
     <t>i2c.o</t>
   </si>
   <si>
-    <t>tim.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_timebase_tim.o</t>
   </si>
   <si>
     <t>cordic.o</t>
   </si>
   <si>
+    <t>dev_motor.o</t>
+  </si>
+  <si>
     <t>thread_management.o</t>
   </si>
   <si>
@@ -77,124 +89,328 @@
     <t>port.o</t>
   </si>
   <si>
+    <t>motor_control.o</t>
+  </si>
+  <si>
+    <t>foc_core.o</t>
+  </si>
+  <si>
     <t>system_stm32g4xx.o</t>
   </si>
   <si>
     <t>app_freertos.o</t>
   </si>
   <si>
+    <t>stm32g4xx_hal_tim.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_adc.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_tim.o</t>
+    <t>stm32g4xx_hal_uart.o</t>
+  </si>
+  <si>
+    <t>arm_cortexM4lf_math.lib</t>
   </si>
   <si>
     <t>stm32g4xx_hal_adc_ex.o</t>
   </si>
   <si>
+    <t>arm_common_tables.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_rcc.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_uart.o</t>
+    <t>motion_param.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_spi.o</t>
+  </si>
+  <si>
+    <t>m_wm.l</t>
+  </si>
+  <si>
+    <t>dev_motor_phase_current.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_fdcan.o</t>
   </si>
   <si>
+    <t>multiturn_counter.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_rcc_ex.o</t>
   </si>
   <si>
+    <t>stm32g4xx_hal_dma.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_tim_ex.o</t>
+  </si>
+  <si>
+    <t>dev_mt6835.o</t>
+  </si>
+  <si>
+    <t>cascade_control.o</t>
+  </si>
+  <si>
+    <t>system_state.o</t>
+  </si>
+  <si>
+    <t>dev_half_bridge.o</t>
+  </si>
+  <si>
+    <t>fz_wm.l</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_gpio.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_tim_ex.o</t>
+    <t>drv_tim.o</t>
+  </si>
+  <si>
+    <t>sinf.o</t>
+  </si>
+  <si>
+    <t>rredf.o</t>
+  </si>
+  <si>
+    <t>pid_core.o</t>
+  </si>
+  <si>
+    <t>ctrl_transition.o</t>
+  </si>
+  <si>
+    <t>initio.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_uart_ex.o</t>
   </si>
   <si>
+    <t>current_loop.o</t>
+  </si>
+  <si>
     <t>gpio.o</t>
   </si>
   <si>
+    <t>fseek.o</t>
+  </si>
+  <si>
+    <t>frem_clz.o</t>
+  </si>
+  <si>
+    <t>stdio.o</t>
+  </si>
+  <si>
     <t>lludivv7m.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_spi.o</t>
+    <t>fopen.o</t>
+  </si>
+  <si>
+    <t>main.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_pwr_ex.o</t>
   </si>
   <si>
-    <t>main.o</t>
+    <t>drv_spi.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_i2c.o</t>
   </si>
   <si>
+    <t>_printf_intcommon.o</t>
+  </si>
+  <si>
+    <t>fmodf.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_i2c_ex.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_cortex.o</t>
   </si>
   <si>
+    <t>roundf.o</t>
+  </si>
+  <si>
+    <t>arm_cos_f32.o</t>
+  </si>
+  <si>
+    <t>arm_sin_f32.o</t>
+  </si>
+  <si>
+    <t>drv_adc.o</t>
+  </si>
+  <si>
+    <t>fnaninf.o</t>
+  </si>
+  <si>
+    <t>init_alloc.o</t>
+  </si>
+  <si>
     <t>list.o</t>
   </si>
   <si>
+    <t>stm32g4xx_it.o</t>
+  </si>
+  <si>
+    <t>dev_config.o</t>
+  </si>
+  <si>
+    <t>_printf_dec.o</t>
+  </si>
+  <si>
+    <t>sys_io.o</t>
+  </si>
+  <si>
+    <t>drv_gpio.o</t>
+  </si>
+  <si>
+    <t>floorf.o</t>
+  </si>
+  <si>
+    <t>__printf.o</t>
+  </si>
+  <si>
     <t>rt_memcpy_w.o</t>
   </si>
   <si>
-    <t>stm32g4xx_it.o</t>
+    <t>frnd.o</t>
+  </si>
+  <si>
+    <t>motor_param.o</t>
+  </si>
+  <si>
+    <t>h1_alloc.o</t>
   </si>
   <si>
     <t>cmsis_os.o</t>
   </si>
   <si>
+    <t>assert_report.o</t>
+  </si>
+  <si>
+    <t>_printf_str.o</t>
+  </si>
+  <si>
+    <t>defsig_rtmem_inner.o</t>
+  </si>
+  <si>
     <t>rt_memclr_w.o</t>
   </si>
   <si>
+    <t>h1_free.o</t>
+  </si>
+  <si>
+    <t>fclose.o</t>
+  </si>
+  <si>
+    <t>dma.o</t>
+  </si>
+  <si>
     <t>sys_stackheap_outer.o</t>
   </si>
   <si>
+    <t>llsdiv.o</t>
+  </si>
+  <si>
+    <t>setvbuf.o</t>
+  </si>
+  <si>
+    <t>ftell.o</t>
+  </si>
+  <si>
+    <t>strlen.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_msp.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_cordic.o</t>
+  </si>
+  <si>
+    <t>h1_extend.o</t>
+  </si>
+  <si>
+    <t>defsig_rtred_inner.o</t>
+  </si>
+  <si>
+    <t>__scatter.o</t>
+  </si>
+  <si>
+    <t>control_irq.o</t>
+  </si>
+  <si>
+    <t>defsig_general.o</t>
+  </si>
+  <si>
+    <t>_printf_char_common.o</t>
+  </si>
+  <si>
     <t>drv_dwt_timer.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_msp.o</t>
-  </si>
-  <si>
-    <t>control_irq.o</t>
+    <t>_printf_char.o</t>
+  </si>
+  <si>
+    <t>user_interface.o</t>
+  </si>
+  <si>
+    <t>funder.o</t>
+  </si>
+  <si>
+    <t>fpclassifyf.o</t>
+  </si>
+  <si>
+    <t>_printf_char_file.o</t>
+  </si>
+  <si>
+    <t>thread_idle.o</t>
+  </si>
+  <si>
+    <t>thread_control.o</t>
+  </si>
+  <si>
+    <t>__scatter_zi.o</t>
+  </si>
+  <si>
+    <t>thread_period.o</t>
+  </si>
+  <si>
+    <t>thread_display.o</t>
   </si>
   <si>
     <t>thread_commun.o</t>
   </si>
   <si>
-    <t>__scatter.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_cordic.o</t>
-  </si>
-  <si>
-    <t>thread_idle.o</t>
-  </si>
-  <si>
-    <t>thread_control.o</t>
-  </si>
-  <si>
-    <t>__scatter_zi.o</t>
-  </si>
-  <si>
-    <t>thread_period.o</t>
-  </si>
-  <si>
-    <t>thread_display.o</t>
-  </si>
-  <si>
     <t>__scatter_copy.o</t>
   </si>
   <si>
+    <t>noretval__2printf.o</t>
+  </si>
+  <si>
+    <t>_rserrno.o</t>
+  </si>
+  <si>
+    <t>libinit2.o</t>
+  </si>
+  <si>
     <t>exit.o</t>
   </si>
   <si>
-    <t>user_interface.o</t>
+    <t>sys_wrch.o</t>
+  </si>
+  <si>
+    <t>h1_init.o</t>
+  </si>
+  <si>
+    <t>defsig_rtred_outer.o</t>
+  </si>
+  <si>
+    <t>defsig_rtmem_outer.o</t>
   </si>
   <si>
     <t>sys_exit.o</t>
@@ -203,43 +419,58 @@
     <t>__rtentry2.o</t>
   </si>
   <si>
-    <t>fz_wm.l</t>
-  </si>
-  <si>
     <t>fpinit.o</t>
   </si>
   <si>
     <t>rtexit2.o</t>
   </si>
   <si>
+    <t>defsig_exit.o</t>
+  </si>
+  <si>
+    <t>rt_errno_addr_intlibspace.o</t>
+  </si>
+  <si>
+    <t>ferror.o</t>
+  </si>
+  <si>
     <t>__main.o</t>
   </si>
   <si>
-    <t>libinit2.o</t>
+    <t>libshutdown2.o</t>
   </si>
   <si>
     <t>heapauxi.o</t>
   </si>
   <si>
+    <t>_printf_s.o</t>
+  </si>
+  <si>
+    <t>_printf_d.o</t>
+  </si>
+  <si>
     <t>__rtentry4.o</t>
   </si>
   <si>
+    <t>hguard.o</t>
+  </si>
+  <si>
+    <t>_printf_percent_end.o</t>
+  </si>
+  <si>
     <t>use_no_semi.o</t>
   </si>
   <si>
     <t>rtexit.o</t>
   </si>
   <si>
-    <t>libshutdown2.o</t>
-  </si>
-  <si>
     <t>libshutdown.o</t>
   </si>
   <si>
     <t>libinit.o</t>
   </si>
   <si>
-    <t>vofa.o</t>
+    <t>drv_usart.o</t>
   </si>
   <si>
     <t>File_name</t>
@@ -359,73 +590,91 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$76</c:f>
+              <c:f>ram_percent!$A$3:$A$153</c:f>
               <c:strCache>
-                <c:ptCount val="74"/>
+                <c:ptCount val="151"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
+                  <c:v>c_w.l</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>pid_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>usart.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>tasks.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>stdio_streams.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>tim.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>drv_rtos.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>spi.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>dev_dwt_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>tasks.o</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>drv_rtos.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>spi.o</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>usart.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="14">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>c_w.l</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="15">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>dev_dwt_counter.o</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="16">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>tim.o</c:v>
-                </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="18">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="19">
+                  <c:v>dev_motor.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
+                  <c:v>motor_control.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>foc_core.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="26">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="150">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -433,74 +682,92 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$76</c:f>
+              <c:f>ram_percent!$B$3:$B$153</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="151"/>
                 <c:pt idx="0">
-                  <c:v>44.31753158569336</c:v>
+                  <c:v>71.16660308837891</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.93032646179199</c:v>
+                  <c:v>7.213768482208252</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.510565280914307</c:v>
+                  <c:v>6.658863544464111</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.683038234710693</c:v>
+                  <c:v>1.976850032806397</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.283266544342041</c:v>
+                  <c:v>1.560671091079712</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.198172569274902</c:v>
+                  <c:v>1.543330311775208</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.85551118850708</c:v>
+                  <c:v>1.47396719455719</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.113078355789185</c:v>
+                  <c:v>1.300559282302856</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.42775559425354</c:v>
+                  <c:v>1.144492149353027</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.370645403862</c:v>
+                  <c:v>0.9884250164031982</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.370645403862</c:v>
+                  <c:v>0.9710842370986939</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.256424903869629</c:v>
+                  <c:v>0.8670395016670227</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.199314713478088</c:v>
+                  <c:v>0.5549052953720093</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.085094213485718</c:v>
+                  <c:v>0.4682013392448425</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.085094213485718</c:v>
+                  <c:v>0.4335197508335114</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.5711022019386292</c:v>
+                  <c:v>0.416178971529007</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.2855511009693146</c:v>
+                  <c:v>0.364156574010849</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.1713306754827499</c:v>
+                  <c:v>0.3294750154018402</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1713306754827499</c:v>
+                  <c:v>0.1734078973531723</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.05711022391915321</c:v>
+                  <c:v>0.09970954060554504</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.05711022391915321</c:v>
-                </c:pt>
-                <c:pt idx="73">
+                  <c:v>0.08670394867658615</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.05202237144112587</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.05202237144112587</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.03468158096075058</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.03468158096075058</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.01734079048037529</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.01734079048037529</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -568,229 +835,460 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$76</c:f>
+              <c:f>flash_percent!$A$3:$A$153</c:f>
               <c:strCache>
-                <c:ptCount val="74"/>
+                <c:ptCount val="151"/>
                 <c:pt idx="0">
-                  <c:v>stm32g4xx_hal_adc.o</c:v>
+                  <c:v>c_w.l</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>stm32g4xx_hal_tim.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>stm32g4xx_hal_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>stm32g4xx_hal_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>arm_cortexM4lf_math.lib</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>stm32g4xx_hal_adc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>arm_common_tables.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>motion_param.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>stm32g4xx_hal_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="10">
+                  <c:v>stm32g4xx_hal_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>m_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>motor_control.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>dev_motor_phase_current.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>foc_core.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>stm32g4xx_hal_fdcan.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>multiturn_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>pid_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>tim.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>stm32g4xx_hal_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>stm32g4xx_hal_tim_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>port.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>dev_mt6835.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>cascade_control.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>system_state.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>dev_half_bridge.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>startup_stm32g474xx.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>heap_4.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>fz_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>dev_motor.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>stm32g4xx_hal_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>stm32g4xx_hal_fdcan.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>c_w.l</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>stm32g4xx_hal_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>startup_stm32g474xx.o</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>heap_4.o</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>tim.o</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>stm32g4xx_hal_tim_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="34">
+                  <c:v>drv_tim.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>sinf.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>rredf.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>pid_core.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>usart.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="40">
+                  <c:v>ctrl_transition.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>initio.o</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="43">
+                  <c:v>current_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="45">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="46">
+                  <c:v>fseek.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>frem_clz.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>stdio.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>lludivv7m.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>stm32g4xx_hal_spi.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>usart.o</c:v>
-                </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="50">
+                  <c:v>fopen.o</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
-                  <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="54">
+                  <c:v>drv_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>stm32g4xx_hal_i2c.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
-                  <c:v>stm32g4xx_hal_i2c.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="57">
+                  <c:v>_printf_intcommon.o</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>fmodf.o</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="60">
+                  <c:v>drv_rtos.o</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="62">
+                  <c:v>roundf.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>arm_cos_f32.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>arm_sin_f32.o</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>drv_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>fnaninf.o</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>init_alloc.o</c:v>
+                </c:pt>
+                <c:pt idx="68">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="69">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
-                  <c:v>drv_rtos.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="70">
+                  <c:v>stm32g4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>dev_config.o</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>_printf_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>dev_dwt_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>sys_io.o</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>drv_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>floorf.o</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>__printf.o</c:v>
+                </c:pt>
+                <c:pt idx="78">
                   <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
-                  <c:v>dev_dwt_counter.o</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>stm32g4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="79">
+                  <c:v>frnd.o</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>motor_param.o</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>h1_alloc.o</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>cmsis_os.o</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>assert_report.o</c:v>
+                </c:pt>
+                <c:pt idx="84">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
-                  <c:v>cmsis_os.o</c:v>
-                </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="85">
+                  <c:v>_printf_str.o</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>defsig_rtmem_inner.o</c:v>
+                </c:pt>
+                <c:pt idx="87">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="88">
+                  <c:v>h1_free.o</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>fclose.o</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="91">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="92">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="93">
+                  <c:v>llsdiv.o</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>setvbuf.o</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="96">
+                  <c:v>ftell.o</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>strlen.o</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>stm32g4xx_hal_msp.o</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>stm32g4xx_hal_cordic.o</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>h1_extend.o</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>defsig_rtred_inner.o</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>__scatter.o</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>control_irq.o</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>defsig_general.o</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>_printf_char_common.o</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
-                  <c:v>stm32g4xx_hal_msp.o</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>control_irq.o</c:v>
-                </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="107">
+                  <c:v>_printf_char.o</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>system_stm32g4xx.o</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>user_interface.o</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>funder.o</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>fpclassifyf.o</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>_printf_char_file.o</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>thread_idle.o</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>thread_control.o</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>__scatter_zi.o</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>thread_period.o</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>thread_display.o</c:v>
+                </c:pt>
+                <c:pt idx="118">
                   <c:v>thread_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
-                  <c:v>__scatter.o</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>stm32g4xx_hal_cordic.o</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>system_stm32g4xx.o</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>thread_idle.o</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>thread_control.o</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>__scatter_zi.o</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>thread_period.o</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>thread_display.o</c:v>
-                </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="119">
                   <c:v>__scatter_copy.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="120">
+                  <c:v>noretval__2printf.o</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>_rserrno.o</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>libinit2.o</c:v>
+                </c:pt>
+                <c:pt idx="123">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
-                  <c:v>user_interface.o</c:v>
-                </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="124">
+                  <c:v>sys_wrch.o</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>h1_init.o</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>defsig_rtred_outer.o</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>defsig_rtmem_outer.o</c:v>
+                </c:pt>
+                <c:pt idx="128">
                   <c:v>sys_exit.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="129">
+                  <c:v>stdio_streams.o</c:v>
+                </c:pt>
+                <c:pt idx="130">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
-                  <c:v>fz_wm.l</c:v>
-                </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="131">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="132">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="133">
+                  <c:v>defsig_exit.o</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>rt_errno_addr_intlibspace.o</c:v>
+                </c:pt>
+                <c:pt idx="135">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="136">
+                  <c:v>ferror.o</c:v>
+                </c:pt>
+                <c:pt idx="137">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
-                  <c:v>libinit2.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="138">
+                  <c:v>libshutdown2.o</c:v>
+                </c:pt>
+                <c:pt idx="139">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="140">
+                  <c:v>_printf_s.o</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>_printf_d.o</c:v>
+                </c:pt>
+                <c:pt idx="142">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="143">
+                  <c:v>hguard.o</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>_printf_percent_end.o</c:v>
+                </c:pt>
+                <c:pt idx="145">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="146">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
-                  <c:v>libshutdown2.o</c:v>
-                </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="147">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="148">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
-                  <c:v>vofa.o</c:v>
-                </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="149">
+                  <c:v>drv_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -798,230 +1296,461 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$76</c:f>
+              <c:f>flash_percent!$B$3:$B$153</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="74"/>
+                <c:ptCount val="151"/>
                 <c:pt idx="0">
-                  <c:v>10.9424638748169</c:v>
+                  <c:v>6.487202167510986</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.724673271179199</c:v>
+                  <c:v>5.865695953369141</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.968584537506104</c:v>
+                  <c:v>5.11179780960083</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.712672233581543</c:v>
+                  <c:v>4.379964828491211</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.415460586547852</c:v>
+                  <c:v>4.317446231842041</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.168372631072998</c:v>
+                  <c:v>4.037952423095703</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.553476810455322</c:v>
+                  <c:v>3.773168563842773</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.032827377319336</c:v>
+                  <c:v>3.493674516677856</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.388633966445923</c:v>
+                  <c:v>3.320829629898071</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.150370597839356</c:v>
+                  <c:v>2.765519380569458</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.053300380706787</c:v>
+                  <c:v>2.563253879547119</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.532650947570801</c:v>
+                  <c:v>2.372021198272705</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.364984035491943</c:v>
+                  <c:v>2.210208892822266</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.223791122436523</c:v>
+                  <c:v>2.177110910415649</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.994352221488953</c:v>
+                  <c:v>1.982200622558594</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.614895820617676</c:v>
+                  <c:v>1.813033223152161</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.447229027748108</c:v>
+                  <c:v>1.529861688613892</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.314860582351685</c:v>
+                  <c:v>1.452633142471314</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.200141191482544</c:v>
+                  <c:v>1.441600441932678</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.111895561218262</c:v>
+                  <c:v>1.390114784240723</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.050123572349548</c:v>
+                  <c:v>1.3643718957901</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.032474398612976</c:v>
+                  <c:v>1.32391881942749</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.006000757217407</c:v>
+                  <c:v>1.312886118888855</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.9707024097442627</c:v>
+                  <c:v>1.287143230438232</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.900105893611908</c:v>
+                  <c:v>1.217269778251648</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.8559830784797669</c:v>
+                  <c:v>1.202559590339661</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.8295093774795532</c:v>
+                  <c:v>1.147396326065064</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.8295093774795532</c:v>
+                  <c:v>0.985584020614624</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.7412636876106262</c:v>
+                  <c:v>0.948808491230011</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.6971408128738403</c:v>
+                  <c:v>0.9414533972740173</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.6088951826095581</c:v>
+                  <c:v>0.9010003209114075</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.600070595741272</c:v>
+                  <c:v>0.8476758003234863</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.5824214816093445</c:v>
+                  <c:v>0.8311268091201782</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4412283897399902</c:v>
+                  <c:v>0.8090614676475525</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4412283897399902</c:v>
+                  <c:v>0.7538982033729553</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.388280987739563</c:v>
+                  <c:v>0.7355104684829712</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3706318438053131</c:v>
+                  <c:v>0.6840246915817261</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.361807256937027</c:v>
+                  <c:v>0.6729920506477356</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3441581428050995</c:v>
+                  <c:v>0.6325389742851257</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3353335559368134</c:v>
+                  <c:v>0.6104736924171448</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3265089988708496</c:v>
+                  <c:v>0.5847308039665222</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.3088598549365997</c:v>
+                  <c:v>0.5736981630325317</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2823861539363861</c:v>
+                  <c:v>0.5663430690765381</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2647370398044586</c:v>
+                  <c:v>0.5111797451972961</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2647370398044586</c:v>
+                  <c:v>0.5001471042633057</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2470878958702087</c:v>
+                  <c:v>0.4633715748786926</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2294387519359589</c:v>
+                  <c:v>0.456016480922699</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2294387519359589</c:v>
+                  <c:v>0.4486613571643829</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1941404938697815</c:v>
+                  <c:v>0.4413062632083893</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1411930769681931</c:v>
+                  <c:v>0.4376287162303925</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1411930769681931</c:v>
+                  <c:v>0.4339511692523956</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1235439479351044</c:v>
+                  <c:v>0.4302736222743988</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1235439479351044</c:v>
+                  <c:v>0.4045307338237763</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1235439479351044</c:v>
+                  <c:v>0.4045307338237763</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1147193759679794</c:v>
+                  <c:v>0.4045307338237763</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.07942111045122147</c:v>
+                  <c:v>0.3751103281974793</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.06177197396755219</c:v>
+                  <c:v>0.3456899225711823</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.05294740572571755</c:v>
+                  <c:v>0.3273021578788757</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.05294740572571755</c:v>
+                  <c:v>0.3236245810985565</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.0441228374838829</c:v>
+                  <c:v>0.3236245810985565</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.0441228374838829</c:v>
+                  <c:v>0.2942041754722595</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.0441228374838829</c:v>
+                  <c:v>0.2905266284942627</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.03529826924204826</c:v>
+                  <c:v>0.283171534538269</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.03529826924204826</c:v>
+                  <c:v>0.2794939577579498</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.02647370286285877</c:v>
+                  <c:v>0.2647837698459625</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.02647370286285877</c:v>
+                  <c:v>0.2611061930656433</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.02647370286285877</c:v>
+                  <c:v>0.2574286460876465</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.008824567310512066</c:v>
+                  <c:v>0.2537510991096497</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.008824567310512066</c:v>
+                  <c:v>0.2537510991096497</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.008824567310512066</c:v>
+                  <c:v>0.2500735521316528</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.008824567310512066</c:v>
+                  <c:v>0.242718443274498</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.008824567310512066</c:v>
+                  <c:v>0.2224919050931931</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.008824567310512066</c:v>
+                  <c:v>0.2206531316041946</c:v>
                 </c:pt>
                 <c:pt idx="73">
+                  <c:v>0.2206531316041946</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.209620475769043</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.209620475769043</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.2059429287910461</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.1912327110767365</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.1838776171207428</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.176522508263588</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.176522508263588</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.1728449612855911</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.1544571965932846</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.1544571965932846</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.1544571965932846</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.1507796347141266</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.1471020877361298</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.1434245407581329</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.1434245407581329</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.1397469788789749</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.1397469788789749</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.1397469788789749</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.1360694319009781</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.1323918849229813</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.1287143230438232</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.1287143230438232</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.121359221637249</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.1140041202306747</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.1103265658020973</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.09929390996694565</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.09561635553836823</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.09561635553836823</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.09561635553836823</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.09561635553836823</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.0919388085603714</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.08826125413179398</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.08826125413179398</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.08090614527463913</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.08090614527463913</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.0772285982966423</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.06987348943948746</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.06987348943948746</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.06619594246149063</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.05884083732962608</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.05884083732962608</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.05148573219776154</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.05148573219776154</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.05148573219776154</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.05148573219776154</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.04780817776918411</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.04413062706589699</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.04045307263731957</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.03309797123074532</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.03309797123074532</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.02574286609888077</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.02574286609888077</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.02574286609888077</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.02574286609888077</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.02206531353294849</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.02206531353294849</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.02206531353294849</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.01838776096701622</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.01838776096701622</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.01838776096701622</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.01471020933240652</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.01471020933240652</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.01471020933240652</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.01471020933240652</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.01103265676647425</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.01103265676647425</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.01103265676647425</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.01103265676647425</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.01103265676647425</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.00735510466620326</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.00735510466620326</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.00367755233310163</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.00367755233310163</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.00367755233310163</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.00367755233310163</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.00367755233310163</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1126,8 +1855,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H76" totalsRowCount="1">
-  <autoFilter ref="A2:H75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H153" totalsRowCount="1">
+  <autoFilter ref="A2:H152"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1143,8 +1872,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H76" totalsRowCount="1">
-  <autoFilter ref="A2:H75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H153" totalsRowCount="1">
+  <autoFilter ref="A2:H152"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1444,7 +2173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1457,28 +2186,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1486,16 +2215,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>44.31753158569336</v>
+        <v>71.16660308837891</v>
       </c>
       <c r="C3" s="1">
-        <v>3104</v>
+        <v>16416</v>
       </c>
       <c r="D3" s="1">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E3" s="1">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -1504,7 +2233,7 @@
         <v>32</v>
       </c>
       <c r="H3" s="1">
-        <v>3072</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1512,25 +2241,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>21.93032646179199</v>
+        <v>7.213768482208252</v>
       </c>
       <c r="C4" s="1">
-        <v>1536</v>
+        <v>1664</v>
       </c>
       <c r="D4" s="1">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="E4" s="1">
-        <v>64</v>
+        <v>516</v>
       </c>
       <c r="F4" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>1536</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1538,25 +2267,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>6.510565280914307</v>
+        <v>6.658863544464111</v>
       </c>
       <c r="C5" s="1">
-        <v>456</v>
+        <v>1536</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>456</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1564,25 +2293,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>4.683038234710693</v>
+        <v>1.976850032806397</v>
       </c>
       <c r="C6" s="1">
-        <v>328</v>
+        <v>456</v>
       </c>
       <c r="D6" s="1">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>1028</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>324</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1590,25 +2319,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.283266544342041</v>
+        <v>1.560671091079712</v>
       </c>
       <c r="C7" s="1">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="D7" s="1">
-        <v>1454</v>
+        <v>3528</v>
       </c>
       <c r="E7" s="1">
-        <v>1394</v>
+        <v>3504</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="H7" s="1">
-        <v>240</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1616,25 +2345,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.198172569274902</v>
+        <v>1.543330311775208</v>
       </c>
       <c r="C8" s="1">
-        <v>224</v>
+        <v>356</v>
       </c>
       <c r="D8" s="1">
-        <v>132</v>
+        <v>790</v>
       </c>
       <c r="E8" s="1">
-        <v>132</v>
+        <v>434</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="1">
-        <v>224</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1642,16 +2371,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.85551118850708</v>
+        <v>1.47396719455719</v>
       </c>
       <c r="C9" s="1">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="D9" s="1">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="E9" s="1">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1660,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>200</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1668,25 +2397,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.113078355789185</v>
+        <v>1.300559282302856</v>
       </c>
       <c r="C10" s="1">
-        <v>148</v>
+        <v>300</v>
       </c>
       <c r="D10" s="1">
-        <v>228</v>
+        <v>1504</v>
       </c>
       <c r="E10" s="1">
-        <v>228</v>
+        <v>1444</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H10" s="1">
-        <v>148</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1694,25 +2423,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.42775559425354</v>
+        <v>1.144492149353027</v>
       </c>
       <c r="C11" s="1">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="D11" s="1">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1720,16 +2449,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.370645403862</v>
+        <v>0.9884250164031982</v>
       </c>
       <c r="C12" s="1">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="D12" s="1">
-        <v>692</v>
+        <v>756</v>
       </c>
       <c r="E12" s="1">
-        <v>692</v>
+        <v>756</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1738,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>96</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1746,16 +2475,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.370645403862</v>
+        <v>0.9710842370986939</v>
       </c>
       <c r="C13" s="1">
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="D13" s="1">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="E13" s="1">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1764,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>96</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1772,16 +2501,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>1.256424903869629</v>
+        <v>0.8670395016670227</v>
       </c>
       <c r="C14" s="1">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="D14" s="1">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="E14" s="1">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1790,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>88</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1798,16 +2527,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>1.199314713478088</v>
+        <v>0.5549052953720093</v>
       </c>
       <c r="C15" s="1">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="D15" s="1">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="E15" s="1">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1816,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1824,16 +2553,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>1.085094213485718</v>
+        <v>0.4682013392448425</v>
       </c>
       <c r="C16" s="1">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="D16" s="1">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="E16" s="1">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1842,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>76</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1850,16 +2579,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>1.085094213485718</v>
+        <v>0.4335197508335114</v>
       </c>
       <c r="C17" s="1">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="D17" s="1">
-        <v>136</v>
+        <v>220</v>
       </c>
       <c r="E17" s="1">
-        <v>136</v>
+        <v>220</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1868,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1876,16 +2605,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.5711022019386292</v>
+        <v>0.416178971529007</v>
       </c>
       <c r="C18" s="1">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="D18" s="1">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1894,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>40</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1902,16 +2631,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.2855511009693146</v>
+        <v>0.364156574010849</v>
       </c>
       <c r="C19" s="1">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="D19" s="1">
-        <v>188</v>
+        <v>252</v>
       </c>
       <c r="E19" s="1">
-        <v>188</v>
+        <v>252</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1920,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>20</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1928,25 +2657,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.1713306754827499</v>
+        <v>0.3294750154018402</v>
       </c>
       <c r="C20" s="1">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="D20" s="1">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="E20" s="1">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1954,25 +2683,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.1713306754827499</v>
+        <v>0.1734078973531723</v>
       </c>
       <c r="C21" s="1">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D21" s="1">
-        <v>714</v>
+        <v>76</v>
       </c>
       <c r="E21" s="1">
-        <v>702</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1980,22 +2709,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.05711022391915321</v>
+        <v>0.09970954060554504</v>
       </c>
       <c r="C22" s="1">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D22" s="1">
-        <v>44</v>
+        <v>461</v>
       </c>
       <c r="E22" s="1">
-        <v>16</v>
+        <v>426</v>
       </c>
       <c r="F22" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G22" s="1">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -2006,56 +2735,212 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.05711022391915321</v>
+        <v>0.08670394867658615</v>
       </c>
       <c r="C23" s="1">
+        <v>20</v>
+      </c>
+      <c r="D23" s="1">
+        <v>188</v>
+      </c>
+      <c r="E23" s="1">
+        <v>188</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.05202237144112587</v>
+      </c>
+      <c r="C24" s="1">
+        <v>12</v>
+      </c>
+      <c r="D24" s="1">
+        <v>70</v>
+      </c>
+      <c r="E24" s="1">
+        <v>58</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>12</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.05202237144112587</v>
+      </c>
+      <c r="C25" s="1">
+        <v>12</v>
+      </c>
+      <c r="D25" s="1">
+        <v>714</v>
+      </c>
+      <c r="E25" s="1">
+        <v>702</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.03468158096075058</v>
+      </c>
+      <c r="C26" s="1">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1202</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1014</v>
+      </c>
+      <c r="F26" s="1">
+        <v>180</v>
+      </c>
+      <c r="G26" s="1">
+        <v>8</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.03468158096075058</v>
+      </c>
+      <c r="C27" s="1">
+        <v>8</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1078</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1070</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>8</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.01734079048037529</v>
+      </c>
+      <c r="C28" s="1">
         <v>4</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D28" s="1">
+        <v>44</v>
+      </c>
+      <c r="E28" s="1">
+        <v>16</v>
+      </c>
+      <c r="F28" s="1">
+        <v>24</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.01734079048037529</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4</v>
+      </c>
+      <c r="D29" s="1">
         <v>84</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E29" s="1">
         <v>48</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F29" s="1">
         <v>32</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G29" s="1">
         <v>4</v>
       </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" t="s">
-        <v>76</v>
-      </c>
-      <c r="B76">
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C76">
+      <c r="C153">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D76">
+      <c r="D153">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E76">
+      <c r="E153">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F76">
+      <c r="F153">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G76">
+      <c r="G153">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H76">
+      <c r="H153">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2071,7 +2956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2084,71 +2969,71 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>10.9424638748169</v>
+        <v>6.487202167510986</v>
       </c>
       <c r="C3" s="1">
-        <v>2480</v>
+        <v>3528</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="E3" s="1">
-        <v>2480</v>
+        <v>3504</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2">
-        <v>9.724673271179199</v>
+        <v>5.865695953369141</v>
       </c>
       <c r="C4" s="1">
-        <v>2204</v>
+        <v>3190</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>2204</v>
+        <v>3190</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -2162,19 +3047,19 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2">
-        <v>7.968584537506104</v>
+        <v>5.11179780960083</v>
       </c>
       <c r="C5" s="1">
-        <v>1806</v>
+        <v>2780</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>1806</v>
+        <v>2780</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2188,22 +3073,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B6" s="2">
-        <v>7.712672233581543</v>
+        <v>4.379964828491211</v>
       </c>
       <c r="C6" s="1">
-        <v>1748</v>
+        <v>2382</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>1748</v>
+        <v>2358</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -2214,48 +3099,48 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2">
-        <v>6.415460586547852</v>
+        <v>4.317446231842041</v>
       </c>
       <c r="C7" s="1">
-        <v>1454</v>
+        <v>2348</v>
       </c>
       <c r="D7" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>1394</v>
+        <v>296</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G7" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2">
-        <v>6.168372631072998</v>
+        <v>4.037952423095703</v>
       </c>
       <c r="C8" s="1">
-        <v>1398</v>
+        <v>2196</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>1374</v>
+        <v>2196</v>
       </c>
       <c r="F8" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -2266,45 +3151,45 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2">
-        <v>4.553476810455322</v>
+        <v>3.773168563842773</v>
       </c>
       <c r="C9" s="1">
-        <v>1032</v>
+        <v>2052</v>
       </c>
       <c r="D9" s="1">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>1028</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G9" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2">
-        <v>4.032827377319336</v>
+        <v>3.493674516677856</v>
       </c>
       <c r="C10" s="1">
-        <v>914</v>
+        <v>1900</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>914</v>
+        <v>1900</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -2318,19 +3203,19 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2">
-        <v>3.388633966445923</v>
+        <v>3.320829629898071</v>
       </c>
       <c r="C11" s="1">
-        <v>768</v>
+        <v>1806</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>768</v>
+        <v>1806</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -2344,45 +3229,45 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2">
-        <v>3.150370597839356</v>
+        <v>2.765519380569458</v>
       </c>
       <c r="C12" s="1">
-        <v>714</v>
+        <v>1504</v>
       </c>
       <c r="D12" s="1">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="E12" s="1">
-        <v>702</v>
+        <v>1444</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2">
-        <v>3.053300380706787</v>
+        <v>2.563253879547119</v>
       </c>
       <c r="C13" s="1">
-        <v>692</v>
+        <v>1394</v>
       </c>
       <c r="D13" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>692</v>
+        <v>1394</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2391,27 +3276,27 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2">
-        <v>2.532650947570801</v>
+        <v>2.372021198272705</v>
       </c>
       <c r="C14" s="1">
-        <v>574</v>
+        <v>1290</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>574</v>
+        <v>1258</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2422,97 +3307,97 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2">
-        <v>2.364984035491943</v>
+        <v>2.210208892822266</v>
       </c>
       <c r="C15" s="1">
-        <v>536</v>
+        <v>1202</v>
       </c>
       <c r="D15" s="1">
-        <v>1536</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1">
-        <v>64</v>
+        <v>1014</v>
       </c>
       <c r="F15" s="1">
-        <v>472</v>
+        <v>180</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H15" s="1">
-        <v>1536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2">
-        <v>2.223791122436523</v>
+        <v>2.177110910415649</v>
       </c>
       <c r="C16" s="1">
-        <v>504</v>
+        <v>1184</v>
       </c>
       <c r="D16" s="1">
-        <v>3104</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>472</v>
+        <v>1184</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>3072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2">
-        <v>1.994352221488953</v>
+        <v>1.982200622558594</v>
       </c>
       <c r="C17" s="1">
-        <v>452</v>
+        <v>1078</v>
       </c>
       <c r="D17" s="1">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1">
-        <v>452</v>
+        <v>1070</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H17" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2">
-        <v>1.614895820617676</v>
+        <v>1.813033223152161</v>
       </c>
       <c r="C18" s="1">
-        <v>366</v>
+        <v>986</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>366</v>
+        <v>986</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2526,19 +3411,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2">
-        <v>1.447229027748108</v>
+        <v>1.529861688613892</v>
       </c>
       <c r="C19" s="1">
-        <v>328</v>
+        <v>832</v>
       </c>
       <c r="D19" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>328</v>
+        <v>832</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2547,50 +3432,50 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>1.314860582351685</v>
+        <v>1.452633142471314</v>
       </c>
       <c r="C20" s="1">
-        <v>298</v>
+        <v>790</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E20" s="1">
-        <v>282</v>
+        <v>434</v>
       </c>
       <c r="F20" s="1">
-        <v>16</v>
+        <v>352</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2">
-        <v>1.200141191482544</v>
+        <v>1.441600441932678</v>
       </c>
       <c r="C21" s="1">
-        <v>272</v>
+        <v>784</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>272</v>
+        <v>784</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2604,19 +3489,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B22" s="2">
-        <v>1.111895561218262</v>
+        <v>1.390114784240723</v>
       </c>
       <c r="C22" s="1">
-        <v>252</v>
+        <v>756</v>
       </c>
       <c r="D22" s="1">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="E22" s="1">
-        <v>252</v>
+        <v>756</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2625,24 +3510,24 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>84</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2">
-        <v>1.050123572349548</v>
+        <v>1.3643718957901</v>
       </c>
       <c r="C23" s="1">
-        <v>238</v>
+        <v>742</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>238</v>
+        <v>742</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2656,19 +3541,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2">
-        <v>1.032474398612976</v>
+        <v>1.32391881942749</v>
       </c>
       <c r="C24" s="1">
-        <v>234</v>
+        <v>720</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>234</v>
+        <v>720</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2682,45 +3567,45 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>1.006000757217407</v>
+        <v>1.312886118888855</v>
       </c>
       <c r="C25" s="1">
-        <v>228</v>
+        <v>714</v>
       </c>
       <c r="D25" s="1">
-        <v>148</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1">
-        <v>228</v>
+        <v>702</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H25" s="1">
-        <v>148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2">
-        <v>0.9707024097442627</v>
+        <v>1.287143230438232</v>
       </c>
       <c r="C26" s="1">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="D26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2729,24 +3614,24 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2">
-        <v>0.900105893611908</v>
+        <v>1.217269778251648</v>
       </c>
       <c r="C27" s="1">
-        <v>204</v>
+        <v>662</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>204</v>
+        <v>662</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2760,22 +3645,22 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B28" s="2">
-        <v>0.8559830784797669</v>
+        <v>1.202559590339661</v>
       </c>
       <c r="C28" s="1">
-        <v>194</v>
+        <v>654</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>194</v>
+        <v>318</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -2786,19 +3671,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2">
-        <v>0.8295093774795532</v>
+        <v>1.147396326065064</v>
       </c>
       <c r="C29" s="1">
-        <v>188</v>
+        <v>624</v>
       </c>
       <c r="D29" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>188</v>
+        <v>624</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2807,50 +3692,50 @@
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="B30" s="2">
-        <v>0.8295093774795532</v>
+        <v>0.985584020614624</v>
       </c>
       <c r="C30" s="1">
-        <v>188</v>
+        <v>536</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="E30" s="1">
-        <v>188</v>
+        <v>64</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B31" s="2">
-        <v>0.7412636876106262</v>
+        <v>0.948808491230011</v>
       </c>
       <c r="C31" s="1">
-        <v>168</v>
+        <v>516</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>1664</v>
       </c>
       <c r="E31" s="1">
-        <v>168</v>
+        <v>516</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2859,50 +3744,50 @@
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>0.6971408128738403</v>
+        <v>0.9414533972740173</v>
       </c>
       <c r="C32" s="1">
-        <v>158</v>
+        <v>512</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>16416</v>
       </c>
       <c r="E32" s="1">
-        <v>158</v>
+        <v>480</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B33" s="2">
-        <v>0.6088951826095581</v>
+        <v>0.9010003209114075</v>
       </c>
       <c r="C33" s="1">
-        <v>138</v>
+        <v>490</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>138</v>
+        <v>490</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2916,45 +3801,45 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B34" s="2">
-        <v>0.600070595741272</v>
+        <v>0.8476758003234863</v>
       </c>
       <c r="C34" s="1">
-        <v>136</v>
+        <v>461</v>
       </c>
       <c r="D34" s="1">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="E34" s="1">
-        <v>136</v>
+        <v>426</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H34" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B35" s="2">
-        <v>0.5824214816093445</v>
+        <v>0.8311268091201782</v>
       </c>
       <c r="C35" s="1">
-        <v>132</v>
+        <v>452</v>
       </c>
       <c r="D35" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>132</v>
+        <v>452</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2963,24 +3848,24 @@
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4412283897399902</v>
+        <v>0.8090614676475525</v>
       </c>
       <c r="C36" s="1">
-        <v>100</v>
+        <v>440</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="E36" s="1">
-        <v>100</v>
+        <v>440</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2989,50 +3874,50 @@
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4412283897399902</v>
+        <v>0.7538982033729553</v>
       </c>
       <c r="C37" s="1">
-        <v>100</v>
+        <v>410</v>
       </c>
       <c r="D37" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>100</v>
+        <v>330</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B38" s="2">
-        <v>0.388280987739563</v>
+        <v>0.7355104684829712</v>
       </c>
       <c r="C38" s="1">
-        <v>88</v>
+        <v>400</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>88</v>
+        <v>400</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -3046,25 +3931,25 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3706318438053131</v>
+        <v>0.6840246915817261</v>
       </c>
       <c r="C39" s="1">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="D39" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>48</v>
+        <v>340</v>
       </c>
       <c r="F39" s="1">
         <v>32</v>
       </c>
       <c r="G39" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -3072,19 +3957,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B40" s="2">
-        <v>0.361807256937027</v>
+        <v>0.6729920506477356</v>
       </c>
       <c r="C40" s="1">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3098,19 +3983,19 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3441581428050995</v>
+        <v>0.6325389742851257</v>
       </c>
       <c r="C41" s="1">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E41" s="1">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -3119,24 +4004,24 @@
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3353335559368134</v>
+        <v>0.6104736924171448</v>
       </c>
       <c r="C42" s="1">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="D42" s="1">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E42" s="1">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -3145,24 +4030,24 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>40</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3265089988708496</v>
+        <v>0.5847308039665222</v>
       </c>
       <c r="C43" s="1">
-        <v>74</v>
+        <v>318</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>74</v>
+        <v>318</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3176,25 +4061,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="B44" s="2">
-        <v>0.3088598549365997</v>
+        <v>0.5736981630325317</v>
       </c>
       <c r="C44" s="1">
-        <v>70</v>
+        <v>312</v>
       </c>
       <c r="D44" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>58</v>
+        <v>312</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3202,22 +4087,22 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2823861539363861</v>
+        <v>0.5663430690765381</v>
       </c>
       <c r="C45" s="1">
-        <v>64</v>
+        <v>308</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>64</v>
+        <v>292</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -3228,19 +4113,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2647370398044586</v>
+        <v>0.5111797451972961</v>
       </c>
       <c r="C46" s="1">
-        <v>60</v>
+        <v>278</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>60</v>
+        <v>278</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3254,19 +4139,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2647370398044586</v>
+        <v>0.5001471042633057</v>
       </c>
       <c r="C47" s="1">
-        <v>60</v>
+        <v>272</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>60</v>
+        <v>272</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3280,19 +4165,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2470878958702087</v>
+        <v>0.4633715748786926</v>
       </c>
       <c r="C48" s="1">
-        <v>56</v>
+        <v>252</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E48" s="1">
-        <v>56</v>
+        <v>252</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3301,24 +4186,24 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2294387519359589</v>
+        <v>0.456016480922699</v>
       </c>
       <c r="C49" s="1">
-        <v>52</v>
+        <v>248</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>52</v>
+        <v>248</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3332,19 +4217,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2294387519359589</v>
+        <v>0.4486613571643829</v>
       </c>
       <c r="C50" s="1">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3358,25 +4243,25 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1941404938697815</v>
+        <v>0.4413062632083893</v>
       </c>
       <c r="C51" s="1">
-        <v>44</v>
+        <v>240</v>
       </c>
       <c r="D51" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="F51" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -3384,19 +4269,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1411930769681931</v>
+        <v>0.4376287162303925</v>
       </c>
       <c r="C52" s="1">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3410,19 +4295,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1411930769681931</v>
+        <v>0.4339511692523956</v>
       </c>
       <c r="C53" s="1">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3436,19 +4321,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1235439479351044</v>
+        <v>0.4302736222743988</v>
       </c>
       <c r="C54" s="1">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3462,19 +4347,19 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1235439479351044</v>
+        <v>0.4045307338237763</v>
       </c>
       <c r="C55" s="1">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3488,19 +4373,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1235439479351044</v>
+        <v>0.4045307338237763</v>
       </c>
       <c r="C56" s="1">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="D56" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E56" s="1">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3509,27 +4394,27 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1147193759679794</v>
+        <v>0.4045307338237763</v>
       </c>
       <c r="C57" s="1">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="F57" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
@@ -3540,19 +4425,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B58" s="2">
-        <v>0.07942111045122147</v>
+        <v>0.3751103281974793</v>
       </c>
       <c r="C58" s="1">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3566,19 +4451,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="B59" s="2">
-        <v>0.06177197396755219</v>
+        <v>0.3456899225711823</v>
       </c>
       <c r="C59" s="1">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E59" s="1">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3587,24 +4472,24 @@
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B60" s="2">
-        <v>0.05294740572571755</v>
+        <v>0.3273021578788757</v>
       </c>
       <c r="C60" s="1">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3618,19 +4503,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B61" s="2">
-        <v>0.05294740572571755</v>
+        <v>0.3236245810985565</v>
       </c>
       <c r="C61" s="1">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3644,19 +4529,19 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B62" s="2">
-        <v>0.0441228374838829</v>
+        <v>0.3236245810985565</v>
       </c>
       <c r="C62" s="1">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3670,19 +4555,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="B63" s="2">
-        <v>0.0441228374838829</v>
+        <v>0.2942041754722595</v>
       </c>
       <c r="C63" s="1">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E63" s="1">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3691,24 +4576,24 @@
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B64" s="2">
-        <v>0.0441228374838829</v>
+        <v>0.2905266284942627</v>
       </c>
       <c r="C64" s="1">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3722,19 +4607,19 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="B65" s="2">
-        <v>0.03529826924204826</v>
+        <v>0.283171534538269</v>
       </c>
       <c r="C65" s="1">
-        <v>8</v>
+        <v>154</v>
       </c>
       <c r="D65" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>8</v>
+        <v>154</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3743,24 +4628,24 @@
         <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B66" s="2">
-        <v>0.03529826924204826</v>
+        <v>0.2794939577579498</v>
       </c>
       <c r="C66" s="1">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3774,19 +4659,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B67" s="2">
-        <v>0.02647370286285877</v>
+        <v>0.2647837698459625</v>
       </c>
       <c r="C67" s="1">
-        <v>6</v>
+        <v>144</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>6</v>
+        <v>144</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3800,22 +4685,22 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B68" s="2">
-        <v>0.02647370286285877</v>
+        <v>0.2611061930656433</v>
       </c>
       <c r="C68" s="1">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="F68" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -3826,19 +4711,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B69" s="2">
-        <v>0.02647370286285877</v>
+        <v>0.2574286460876465</v>
       </c>
       <c r="C69" s="1">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3852,19 +4737,19 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B70" s="2">
-        <v>0.008824567310512066</v>
+        <v>0.2537510991096497</v>
       </c>
       <c r="C70" s="1">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3878,19 +4763,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B71" s="2">
-        <v>0.008824567310512066</v>
+        <v>0.2537510991096497</v>
       </c>
       <c r="C71" s="1">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3904,19 +4789,19 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="B72" s="2">
-        <v>0.008824567310512066</v>
+        <v>0.2500735521316528</v>
       </c>
       <c r="C72" s="1">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E72" s="1">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3925,24 +4810,24 @@
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B73" s="2">
-        <v>0.008824567310512066</v>
+        <v>0.242718443274498</v>
       </c>
       <c r="C73" s="1">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -3956,22 +4841,22 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B74" s="2">
-        <v>0.008824567310512066</v>
+        <v>0.2224919050931931</v>
       </c>
       <c r="C74" s="1">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F74" s="1">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
@@ -3982,59 +4867,2061 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="2">
+        <v>0.2206531316041946</v>
+      </c>
+      <c r="C75" s="1">
+        <v>120</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>120</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.2206531316041946</v>
+      </c>
+      <c r="C76" s="1">
+        <v>120</v>
+      </c>
+      <c r="D76" s="1">
+        <v>128</v>
+      </c>
+      <c r="E76" s="1">
+        <v>120</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="2">
+        <v>0.209620475769043</v>
+      </c>
+      <c r="C77" s="1">
+        <v>114</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>102</v>
+      </c>
+      <c r="F77" s="1">
+        <v>12</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="2">
+        <v>0.209620475769043</v>
+      </c>
+      <c r="C78" s="1">
+        <v>114</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1">
+        <v>82</v>
+      </c>
+      <c r="F78" s="1">
+        <v>32</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="2">
+        <v>0.2059429287910461</v>
+      </c>
+      <c r="C79" s="1">
+        <v>112</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1">
+        <v>112</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="2">
+        <v>0.1912327110767365</v>
+      </c>
+      <c r="C80" s="1">
+        <v>104</v>
+      </c>
+      <c r="D80" s="1">
+        <v>0</v>
+      </c>
+      <c r="E80" s="1">
+        <v>104</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="2">
+        <v>0.1838776171207428</v>
+      </c>
+      <c r="C81" s="1">
+        <v>100</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
+        <v>100</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="2">
+        <v>0.176522508263588</v>
+      </c>
+      <c r="C82" s="1">
+        <v>96</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1">
+        <v>96</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="2">
+        <v>0.176522508263588</v>
+      </c>
+      <c r="C83" s="1">
+        <v>96</v>
+      </c>
+      <c r="D83" s="1">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1">
+        <v>96</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="2">
+        <v>0.1728449612855911</v>
+      </c>
+      <c r="C84" s="1">
+        <v>94</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0</v>
+      </c>
+      <c r="E84" s="1">
+        <v>94</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="2">
+        <v>0.1544571965932846</v>
+      </c>
+      <c r="C85" s="1">
+        <v>84</v>
+      </c>
+      <c r="D85" s="1">
+        <v>0</v>
+      </c>
+      <c r="E85" s="1">
+        <v>84</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="2">
+        <v>0.1544571965932846</v>
+      </c>
+      <c r="C86" s="1">
+        <v>84</v>
+      </c>
+      <c r="D86" s="1">
+        <v>0</v>
+      </c>
+      <c r="E86" s="1">
+        <v>84</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B87" s="2">
+        <v>0.1544571965932846</v>
+      </c>
+      <c r="C87" s="1">
+        <v>84</v>
+      </c>
+      <c r="D87" s="1">
+        <v>4</v>
+      </c>
+      <c r="E87" s="1">
+        <v>48</v>
+      </c>
+      <c r="F87" s="1">
+        <v>32</v>
+      </c>
+      <c r="G87" s="1">
+        <v>4</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="2">
+        <v>0.1507796347141266</v>
+      </c>
+      <c r="C88" s="1">
+        <v>82</v>
+      </c>
+      <c r="D88" s="1">
+        <v>0</v>
+      </c>
+      <c r="E88" s="1">
+        <v>82</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="2">
+        <v>0.1471020877361298</v>
+      </c>
+      <c r="C89" s="1">
+        <v>80</v>
+      </c>
+      <c r="D89" s="1">
+        <v>0</v>
+      </c>
+      <c r="E89" s="1">
+        <v>80</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="2">
+        <v>0.1434245407581329</v>
+      </c>
+      <c r="C90" s="1">
+        <v>78</v>
+      </c>
+      <c r="D90" s="1">
+        <v>0</v>
+      </c>
+      <c r="E90" s="1">
+        <v>78</v>
+      </c>
+      <c r="F90" s="1">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="2">
+        <v>0.1434245407581329</v>
+      </c>
+      <c r="C91" s="1">
+        <v>78</v>
+      </c>
+      <c r="D91" s="1">
+        <v>0</v>
+      </c>
+      <c r="E91" s="1">
+        <v>78</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="2">
+        <v>0.1397469788789749</v>
+      </c>
+      <c r="C92" s="1">
+        <v>76</v>
+      </c>
+      <c r="D92" s="1">
+        <v>0</v>
+      </c>
+      <c r="E92" s="1">
+        <v>76</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>0</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" s="2">
+        <v>0.1397469788789749</v>
+      </c>
+      <c r="C93" s="1">
+        <v>76</v>
+      </c>
+      <c r="D93" s="1">
+        <v>0</v>
+      </c>
+      <c r="E93" s="1">
+        <v>76</v>
+      </c>
+      <c r="F93" s="1">
+        <v>0</v>
+      </c>
+      <c r="G93" s="1">
+        <v>0</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" s="2">
+        <v>0.1397469788789749</v>
+      </c>
+      <c r="C94" s="1">
+        <v>76</v>
+      </c>
+      <c r="D94" s="1">
+        <v>40</v>
+      </c>
+      <c r="E94" s="1">
+        <v>76</v>
+      </c>
+      <c r="F94" s="1">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" s="2">
+        <v>0.1360694319009781</v>
+      </c>
+      <c r="C95" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="2">
-        <v>0.008824567310512066</v>
-      </c>
-      <c r="C75" s="1">
+      <c r="D95" s="1">
+        <v>0</v>
+      </c>
+      <c r="E95" s="1">
+        <v>74</v>
+      </c>
+      <c r="F95" s="1">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1">
+        <v>0</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B96" s="2">
+        <v>0.1323918849229813</v>
+      </c>
+      <c r="C96" s="1">
+        <v>72</v>
+      </c>
+      <c r="D96" s="1">
+        <v>0</v>
+      </c>
+      <c r="E96" s="1">
+        <v>72</v>
+      </c>
+      <c r="F96" s="1">
+        <v>0</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" s="2">
+        <v>0.1287143230438232</v>
+      </c>
+      <c r="C97" s="1">
+        <v>70</v>
+      </c>
+      <c r="D97" s="1">
+        <v>0</v>
+      </c>
+      <c r="E97" s="1">
+        <v>70</v>
+      </c>
+      <c r="F97" s="1">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>0</v>
+      </c>
+      <c r="H97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="2">
+        <v>0.1287143230438232</v>
+      </c>
+      <c r="C98" s="1">
+        <v>70</v>
+      </c>
+      <c r="D98" s="1">
+        <v>12</v>
+      </c>
+      <c r="E98" s="1">
+        <v>58</v>
+      </c>
+      <c r="F98" s="1">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1">
+        <v>12</v>
+      </c>
+      <c r="H98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99" s="2">
+        <v>0.121359221637249</v>
+      </c>
+      <c r="C99" s="1">
+        <v>66</v>
+      </c>
+      <c r="D99" s="1">
+        <v>0</v>
+      </c>
+      <c r="E99" s="1">
+        <v>66</v>
+      </c>
+      <c r="F99" s="1">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" s="2">
+        <v>0.1140041202306747</v>
+      </c>
+      <c r="C100" s="1">
+        <v>62</v>
+      </c>
+      <c r="D100" s="1">
+        <v>0</v>
+      </c>
+      <c r="E100" s="1">
+        <v>62</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B101" s="2">
+        <v>0.1103265658020973</v>
+      </c>
+      <c r="C101" s="1">
+        <v>60</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1">
+        <v>60</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>0</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B102" s="2">
+        <v>0.09929390996694565</v>
+      </c>
+      <c r="C102" s="1">
+        <v>54</v>
+      </c>
+      <c r="D102" s="1">
+        <v>0</v>
+      </c>
+      <c r="E102" s="1">
+        <v>54</v>
+      </c>
+      <c r="F102" s="1">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>0</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B103" s="2">
+        <v>0.09561635553836823</v>
+      </c>
+      <c r="C103" s="1">
+        <v>52</v>
+      </c>
+      <c r="D103" s="1">
+        <v>0</v>
+      </c>
+      <c r="E103" s="1">
+        <v>52</v>
+      </c>
+      <c r="F103" s="1">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B104" s="2">
+        <v>0.09561635553836823</v>
+      </c>
+      <c r="C104" s="1">
+        <v>52</v>
+      </c>
+      <c r="D104" s="1">
+        <v>0</v>
+      </c>
+      <c r="E104" s="1">
+        <v>52</v>
+      </c>
+      <c r="F104" s="1">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1">
+        <v>0</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B105" s="2">
+        <v>0.09561635553836823</v>
+      </c>
+      <c r="C105" s="1">
+        <v>52</v>
+      </c>
+      <c r="D105" s="1">
+        <v>0</v>
+      </c>
+      <c r="E105" s="1">
+        <v>52</v>
+      </c>
+      <c r="F105" s="1">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B106" s="2">
+        <v>0.09561635553836823</v>
+      </c>
+      <c r="C106" s="1">
+        <v>52</v>
+      </c>
+      <c r="D106" s="1">
+        <v>0</v>
+      </c>
+      <c r="E106" s="1">
+        <v>52</v>
+      </c>
+      <c r="F106" s="1">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B107" s="2">
+        <v>0.0919388085603714</v>
+      </c>
+      <c r="C107" s="1">
+        <v>50</v>
+      </c>
+      <c r="D107" s="1">
+        <v>0</v>
+      </c>
+      <c r="E107" s="1">
+        <v>50</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B108" s="2">
+        <v>0.08826125413179398</v>
+      </c>
+      <c r="C108" s="1">
+        <v>48</v>
+      </c>
+      <c r="D108" s="1">
+        <v>0</v>
+      </c>
+      <c r="E108" s="1">
+        <v>48</v>
+      </c>
+      <c r="F108" s="1">
+        <v>0</v>
+      </c>
+      <c r="G108" s="1">
+        <v>0</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B109" s="2">
+        <v>0.08826125413179398</v>
+      </c>
+      <c r="C109" s="1">
+        <v>48</v>
+      </c>
+      <c r="D109" s="1">
+        <v>0</v>
+      </c>
+      <c r="E109" s="1">
+        <v>48</v>
+      </c>
+      <c r="F109" s="1">
+        <v>0</v>
+      </c>
+      <c r="G109" s="1">
+        <v>0</v>
+      </c>
+      <c r="H109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B110" s="2">
+        <v>0.08090614527463913</v>
+      </c>
+      <c r="C110" s="1">
+        <v>44</v>
+      </c>
+      <c r="D110" s="1">
+        <v>0</v>
+      </c>
+      <c r="E110" s="1">
+        <v>44</v>
+      </c>
+      <c r="F110" s="1">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1">
+        <v>0</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B111" s="2">
+        <v>0.08090614527463913</v>
+      </c>
+      <c r="C111" s="1">
+        <v>44</v>
+      </c>
+      <c r="D111" s="1">
+        <v>4</v>
+      </c>
+      <c r="E111" s="1">
+        <v>16</v>
+      </c>
+      <c r="F111" s="1">
+        <v>24</v>
+      </c>
+      <c r="G111" s="1">
+        <v>4</v>
+      </c>
+      <c r="H111" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B112" s="2">
+        <v>0.0772285982966423</v>
+      </c>
+      <c r="C112" s="1">
+        <v>42</v>
+      </c>
+      <c r="D112" s="1">
+        <v>0</v>
+      </c>
+      <c r="E112" s="1">
+        <v>42</v>
+      </c>
+      <c r="F112" s="1">
+        <v>0</v>
+      </c>
+      <c r="G112" s="1">
+        <v>0</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="2">
+        <v>0.06987348943948746</v>
+      </c>
+      <c r="C113" s="1">
+        <v>38</v>
+      </c>
+      <c r="D113" s="1">
+        <v>0</v>
+      </c>
+      <c r="E113" s="1">
+        <v>38</v>
+      </c>
+      <c r="F113" s="1">
+        <v>0</v>
+      </c>
+      <c r="G113" s="1">
+        <v>0</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="2">
+        <v>0.06987348943948746</v>
+      </c>
+      <c r="C114" s="1">
+        <v>38</v>
+      </c>
+      <c r="D114" s="1">
+        <v>0</v>
+      </c>
+      <c r="E114" s="1">
+        <v>38</v>
+      </c>
+      <c r="F114" s="1">
+        <v>0</v>
+      </c>
+      <c r="G114" s="1">
+        <v>0</v>
+      </c>
+      <c r="H114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B115" s="2">
+        <v>0.06619594246149063</v>
+      </c>
+      <c r="C115" s="1">
+        <v>36</v>
+      </c>
+      <c r="D115" s="1">
+        <v>0</v>
+      </c>
+      <c r="E115" s="1">
+        <v>36</v>
+      </c>
+      <c r="F115" s="1">
+        <v>0</v>
+      </c>
+      <c r="G115" s="1">
+        <v>0</v>
+      </c>
+      <c r="H115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B116" s="2">
+        <v>0.05884083732962608</v>
+      </c>
+      <c r="C116" s="1">
+        <v>32</v>
+      </c>
+      <c r="D116" s="1">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1">
+        <v>32</v>
+      </c>
+      <c r="F116" s="1">
+        <v>0</v>
+      </c>
+      <c r="G116" s="1">
+        <v>0</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B117" s="2">
+        <v>0.05884083732962608</v>
+      </c>
+      <c r="C117" s="1">
+        <v>32</v>
+      </c>
+      <c r="D117" s="1">
+        <v>0</v>
+      </c>
+      <c r="E117" s="1">
+        <v>32</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0</v>
+      </c>
+      <c r="G117" s="1">
+        <v>0</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B118" s="2">
+        <v>0.05148573219776154</v>
+      </c>
+      <c r="C118" s="1">
+        <v>28</v>
+      </c>
+      <c r="D118" s="1">
+        <v>0</v>
+      </c>
+      <c r="E118" s="1">
+        <v>28</v>
+      </c>
+      <c r="F118" s="1">
+        <v>0</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="2">
+        <v>0.05148573219776154</v>
+      </c>
+      <c r="C119" s="1">
+        <v>28</v>
+      </c>
+      <c r="D119" s="1">
+        <v>0</v>
+      </c>
+      <c r="E119" s="1">
+        <v>28</v>
+      </c>
+      <c r="F119" s="1">
+        <v>0</v>
+      </c>
+      <c r="G119" s="1">
+        <v>0</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B120" s="2">
+        <v>0.05148573219776154</v>
+      </c>
+      <c r="C120" s="1">
+        <v>28</v>
+      </c>
+      <c r="D120" s="1">
+        <v>0</v>
+      </c>
+      <c r="E120" s="1">
+        <v>28</v>
+      </c>
+      <c r="F120" s="1">
+        <v>0</v>
+      </c>
+      <c r="G120" s="1">
+        <v>0</v>
+      </c>
+      <c r="H120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="2">
+        <v>0.05148573219776154</v>
+      </c>
+      <c r="C121" s="1">
+        <v>28</v>
+      </c>
+      <c r="D121" s="1">
+        <v>0</v>
+      </c>
+      <c r="E121" s="1">
+        <v>28</v>
+      </c>
+      <c r="F121" s="1">
+        <v>0</v>
+      </c>
+      <c r="G121" s="1">
+        <v>0</v>
+      </c>
+      <c r="H121" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B122" s="2">
+        <v>0.04780817776918411</v>
+      </c>
+      <c r="C122" s="1">
+        <v>26</v>
+      </c>
+      <c r="D122" s="1">
+        <v>0</v>
+      </c>
+      <c r="E122" s="1">
+        <v>26</v>
+      </c>
+      <c r="F122" s="1">
+        <v>0</v>
+      </c>
+      <c r="G122" s="1">
+        <v>0</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B123" s="2">
+        <v>0.04413062706589699</v>
+      </c>
+      <c r="C123" s="1">
+        <v>24</v>
+      </c>
+      <c r="D123" s="1">
+        <v>0</v>
+      </c>
+      <c r="E123" s="1">
+        <v>24</v>
+      </c>
+      <c r="F123" s="1">
+        <v>0</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B124" s="2">
+        <v>0.04045307263731957</v>
+      </c>
+      <c r="C124" s="1">
+        <v>22</v>
+      </c>
+      <c r="D124" s="1">
+        <v>0</v>
+      </c>
+      <c r="E124" s="1">
+        <v>22</v>
+      </c>
+      <c r="F124" s="1">
+        <v>0</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B125" s="2">
+        <v>0.03309797123074532</v>
+      </c>
+      <c r="C125" s="1">
+        <v>18</v>
+      </c>
+      <c r="D125" s="1">
+        <v>0</v>
+      </c>
+      <c r="E125" s="1">
+        <v>18</v>
+      </c>
+      <c r="F125" s="1">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B126" s="2">
+        <v>0.03309797123074532</v>
+      </c>
+      <c r="C126" s="1">
+        <v>18</v>
+      </c>
+      <c r="D126" s="1">
+        <v>0</v>
+      </c>
+      <c r="E126" s="1">
+        <v>18</v>
+      </c>
+      <c r="F126" s="1">
+        <v>0</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0</v>
+      </c>
+      <c r="H126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="2">
+        <v>0.02574286609888077</v>
+      </c>
+      <c r="C127" s="1">
+        <v>14</v>
+      </c>
+      <c r="D127" s="1">
+        <v>0</v>
+      </c>
+      <c r="E127" s="1">
+        <v>14</v>
+      </c>
+      <c r="F127" s="1">
+        <v>0</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B128" s="2">
+        <v>0.02574286609888077</v>
+      </c>
+      <c r="C128" s="1">
+        <v>14</v>
+      </c>
+      <c r="D128" s="1">
+        <v>0</v>
+      </c>
+      <c r="E128" s="1">
+        <v>14</v>
+      </c>
+      <c r="F128" s="1">
+        <v>0</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B129" s="2">
+        <v>0.02574286609888077</v>
+      </c>
+      <c r="C129" s="1">
+        <v>14</v>
+      </c>
+      <c r="D129" s="1">
+        <v>0</v>
+      </c>
+      <c r="E129" s="1">
+        <v>14</v>
+      </c>
+      <c r="F129" s="1">
+        <v>0</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B130" s="2">
+        <v>0.02574286609888077</v>
+      </c>
+      <c r="C130" s="1">
+        <v>14</v>
+      </c>
+      <c r="D130" s="1">
+        <v>0</v>
+      </c>
+      <c r="E130" s="1">
+        <v>14</v>
+      </c>
+      <c r="F130" s="1">
+        <v>0</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B131" s="2">
+        <v>0.02206531353294849</v>
+      </c>
+      <c r="C131" s="1">
+        <v>12</v>
+      </c>
+      <c r="D131" s="1">
+        <v>0</v>
+      </c>
+      <c r="E131" s="1">
+        <v>12</v>
+      </c>
+      <c r="F131" s="1">
+        <v>0</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B132" s="2">
+        <v>0.02206531353294849</v>
+      </c>
+      <c r="C132" s="1">
+        <v>12</v>
+      </c>
+      <c r="D132" s="1">
+        <v>264</v>
+      </c>
+      <c r="E132" s="1">
+        <v>0</v>
+      </c>
+      <c r="F132" s="1">
+        <v>0</v>
+      </c>
+      <c r="G132" s="1">
+        <v>12</v>
+      </c>
+      <c r="H132" s="1">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" s="2">
+        <v>0.02206531353294849</v>
+      </c>
+      <c r="C133" s="1">
+        <v>12</v>
+      </c>
+      <c r="D133" s="1">
+        <v>0</v>
+      </c>
+      <c r="E133" s="1">
+        <v>12</v>
+      </c>
+      <c r="F133" s="1">
+        <v>0</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B134" s="2">
+        <v>0.01838776096701622</v>
+      </c>
+      <c r="C134" s="1">
+        <v>10</v>
+      </c>
+      <c r="D134" s="1">
+        <v>0</v>
+      </c>
+      <c r="E134" s="1">
+        <v>10</v>
+      </c>
+      <c r="F134" s="1">
+        <v>0</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B135" s="2">
+        <v>0.01838776096701622</v>
+      </c>
+      <c r="C135" s="1">
+        <v>10</v>
+      </c>
+      <c r="D135" s="1">
+        <v>0</v>
+      </c>
+      <c r="E135" s="1">
+        <v>10</v>
+      </c>
+      <c r="F135" s="1">
+        <v>0</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" s="2">
+        <v>0.01838776096701622</v>
+      </c>
+      <c r="C136" s="1">
+        <v>10</v>
+      </c>
+      <c r="D136" s="1">
+        <v>0</v>
+      </c>
+      <c r="E136" s="1">
+        <v>10</v>
+      </c>
+      <c r="F136" s="1">
+        <v>0</v>
+      </c>
+      <c r="G136" s="1">
+        <v>0</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B137" s="2">
+        <v>0.01471020933240652</v>
+      </c>
+      <c r="C137" s="1">
+        <v>8</v>
+      </c>
+      <c r="D137" s="1">
+        <v>0</v>
+      </c>
+      <c r="E137" s="1">
+        <v>8</v>
+      </c>
+      <c r="F137" s="1">
+        <v>0</v>
+      </c>
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B138" s="2">
+        <v>0.01471020933240652</v>
+      </c>
+      <c r="C138" s="1">
+        <v>8</v>
+      </c>
+      <c r="D138" s="1">
+        <v>96</v>
+      </c>
+      <c r="E138" s="1">
+        <v>8</v>
+      </c>
+      <c r="F138" s="1">
+        <v>0</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+      <c r="H138" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2">
+        <v>0.01471020933240652</v>
+      </c>
+      <c r="C139" s="1">
+        <v>8</v>
+      </c>
+      <c r="D139" s="1">
+        <v>0</v>
+      </c>
+      <c r="E139" s="1">
+        <v>8</v>
+      </c>
+      <c r="F139" s="1">
+        <v>0</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2">
+        <v>0.01471020933240652</v>
+      </c>
+      <c r="C140" s="1">
+        <v>8</v>
+      </c>
+      <c r="D140" s="1">
+        <v>0</v>
+      </c>
+      <c r="E140" s="1">
+        <v>8</v>
+      </c>
+      <c r="F140" s="1">
+        <v>0</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2">
+        <v>0.01103265676647425</v>
+      </c>
+      <c r="C141" s="1">
+        <v>6</v>
+      </c>
+      <c r="D141" s="1">
+        <v>0</v>
+      </c>
+      <c r="E141" s="1">
+        <v>6</v>
+      </c>
+      <c r="F141" s="1">
+        <v>0</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2">
+        <v>0.01103265676647425</v>
+      </c>
+      <c r="C142" s="1">
+        <v>6</v>
+      </c>
+      <c r="D142" s="1">
+        <v>0</v>
+      </c>
+      <c r="E142" s="1">
+        <v>6</v>
+      </c>
+      <c r="F142" s="1">
+        <v>0</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2">
+        <v>0.01103265676647425</v>
+      </c>
+      <c r="C143" s="1">
+        <v>6</v>
+      </c>
+      <c r="D143" s="1">
+        <v>0</v>
+      </c>
+      <c r="E143" s="1">
+        <v>6</v>
+      </c>
+      <c r="F143" s="1">
+        <v>0</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+      <c r="H143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2">
+        <v>0.01103265676647425</v>
+      </c>
+      <c r="C144" s="1">
+        <v>6</v>
+      </c>
+      <c r="D144" s="1">
+        <v>0</v>
+      </c>
+      <c r="E144" s="1">
+        <v>6</v>
+      </c>
+      <c r="F144" s="1">
+        <v>0</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2">
+        <v>0.01103265676647425</v>
+      </c>
+      <c r="C145" s="1">
+        <v>6</v>
+      </c>
+      <c r="D145" s="1">
+        <v>0</v>
+      </c>
+      <c r="E145" s="1">
+        <v>6</v>
+      </c>
+      <c r="F145" s="1">
+        <v>0</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+      <c r="H145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2">
+        <v>0.00735510466620326</v>
+      </c>
+      <c r="C146" s="1">
+        <v>4</v>
+      </c>
+      <c r="D146" s="1">
+        <v>0</v>
+      </c>
+      <c r="E146" s="1">
+        <v>4</v>
+      </c>
+      <c r="F146" s="1">
+        <v>0</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2">
+        <v>0.00735510466620326</v>
+      </c>
+      <c r="C147" s="1">
+        <v>4</v>
+      </c>
+      <c r="D147" s="1">
+        <v>0</v>
+      </c>
+      <c r="E147" s="1">
+        <v>4</v>
+      </c>
+      <c r="F147" s="1">
+        <v>0</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+      <c r="H147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2">
+        <v>0.00367755233310163</v>
+      </c>
+      <c r="C148" s="1">
         <v>2</v>
       </c>
-      <c r="D75" s="1">
-        <v>0</v>
-      </c>
-      <c r="E75" s="1">
+      <c r="D148" s="1">
+        <v>0</v>
+      </c>
+      <c r="E148" s="1">
         <v>2</v>
       </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0</v>
-      </c>
-      <c r="H75" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" t="s">
-        <v>76</v>
-      </c>
-      <c r="B76">
+      <c r="F148" s="1">
+        <v>0</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+      <c r="H148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2">
+        <v>0.00367755233310163</v>
+      </c>
+      <c r="C149" s="1">
+        <v>2</v>
+      </c>
+      <c r="D149" s="1">
+        <v>0</v>
+      </c>
+      <c r="E149" s="1">
+        <v>2</v>
+      </c>
+      <c r="F149" s="1">
+        <v>0</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2">
+        <v>0.00367755233310163</v>
+      </c>
+      <c r="C150" s="1">
+        <v>2</v>
+      </c>
+      <c r="D150" s="1">
+        <v>0</v>
+      </c>
+      <c r="E150" s="1">
+        <v>2</v>
+      </c>
+      <c r="F150" s="1">
+        <v>0</v>
+      </c>
+      <c r="G150" s="1">
+        <v>0</v>
+      </c>
+      <c r="H150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2">
+        <v>0.00367755233310163</v>
+      </c>
+      <c r="C151" s="1">
+        <v>2</v>
+      </c>
+      <c r="D151" s="1">
+        <v>0</v>
+      </c>
+      <c r="E151" s="1">
+        <v>2</v>
+      </c>
+      <c r="F151" s="1">
+        <v>0</v>
+      </c>
+      <c r="G151" s="1">
+        <v>0</v>
+      </c>
+      <c r="H151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2">
+        <v>0.00367755233310163</v>
+      </c>
+      <c r="C152" s="1">
+        <v>2</v>
+      </c>
+      <c r="D152" s="1">
+        <v>0</v>
+      </c>
+      <c r="E152" s="1">
+        <v>2</v>
+      </c>
+      <c r="F152" s="1">
+        <v>0</v>
+      </c>
+      <c r="G152" s="1">
+        <v>0</v>
+      </c>
+      <c r="H152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C76">
+      <c r="C153">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D76">
+      <c r="D153">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E76">
+      <c r="E153">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F76">
+      <c r="F153">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G76">
+      <c r="G153">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H76">
+      <c r="H153">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="133">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -26,15 +26,18 @@
     <t>motor_loop.o</t>
   </si>
   <si>
+    <t>dev_commun_uart.o</t>
+  </si>
+  <si>
     <t>startup_stm32g474xx.o</t>
   </si>
   <si>
+    <t>packer_parser.o</t>
+  </si>
+  <si>
     <t>runtime_param.o</t>
   </si>
   <si>
-    <t>c_w.l</t>
-  </si>
-  <si>
     <t>pid_profile.o</t>
   </si>
   <si>
@@ -44,9 +47,6 @@
     <t>tasks.o</t>
   </si>
   <si>
-    <t>stdio_streams.o</t>
-  </si>
-  <si>
     <t>tim.o</t>
   </si>
   <si>
@@ -65,12 +65,12 @@
     <t>fdcan.o</t>
   </si>
   <si>
-    <t>libspace.o</t>
-  </si>
-  <si>
     <t>i2c.o</t>
   </si>
   <si>
+    <t>drv_usart.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_timebase_tim.o</t>
   </si>
   <si>
@@ -83,36 +83,54 @@
     <t>thread_management.o</t>
   </si>
   <si>
+    <t>mc_w.l</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal.o</t>
   </si>
   <si>
     <t>port.o</t>
   </si>
   <si>
+    <t>mvars.o</t>
+  </si>
+  <si>
     <t>motor_control.o</t>
   </si>
   <si>
     <t>foc_core.o</t>
   </si>
   <si>
+    <t>stdout.o</t>
+  </si>
+  <si>
+    <t>errno.o</t>
+  </si>
+  <si>
     <t>system_stm32g4xx.o</t>
   </si>
   <si>
+    <t>jm_proto_uart.o</t>
+  </si>
+  <si>
     <t>app_freertos.o</t>
   </si>
   <si>
+    <t>stm32g4xx_hal_uart.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_tim.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_adc.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_uart.o</t>
-  </si>
-  <si>
     <t>arm_cortexM4lf_math.lib</t>
   </si>
   <si>
+    <t>printfa.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_adc_ex.o</t>
   </si>
   <si>
@@ -125,9 +143,15 @@
     <t>motion_param.o</t>
   </si>
   <si>
+    <t>jm_proto.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_spi.o</t>
   </si>
   <si>
+    <t>mf_w.l</t>
+  </si>
+  <si>
     <t>m_wm.l</t>
   </si>
   <si>
@@ -137,15 +161,15 @@
     <t>stm32g4xx_hal_fdcan.o</t>
   </si>
   <si>
+    <t>stm32g4xx_hal_dma.o</t>
+  </si>
+  <si>
     <t>multiturn_counter.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_rcc_ex.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_dma.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_tim_ex.o</t>
   </si>
   <si>
@@ -161,7 +185,7 @@
     <t>dev_half_bridge.o</t>
   </si>
   <si>
-    <t>fz_wm.l</t>
+    <t>crc16.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_gpio.o</t>
@@ -179,12 +203,12 @@
     <t>pid_core.o</t>
   </si>
   <si>
+    <t>dadd.o</t>
+  </si>
+  <si>
     <t>ctrl_transition.o</t>
   </si>
   <si>
-    <t>initio.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_uart_ex.o</t>
   </si>
   <si>
@@ -194,24 +218,18 @@
     <t>gpio.o</t>
   </si>
   <si>
-    <t>fseek.o</t>
-  </si>
-  <si>
-    <t>frem_clz.o</t>
-  </si>
-  <si>
-    <t>stdio.o</t>
-  </si>
-  <si>
-    <t>lludivv7m.o</t>
-  </si>
-  <si>
-    <t>fopen.o</t>
+    <t>thread_commun.o</t>
   </si>
   <si>
     <t>main.o</t>
   </si>
   <si>
+    <t>dmul.o</t>
+  </si>
+  <si>
+    <t>ddiv.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_pwr_ex.o</t>
   </si>
   <si>
@@ -221,7 +239,10 @@
     <t>stm32g4xx_hal_i2c.o</t>
   </si>
   <si>
-    <t>_printf_intcommon.o</t>
+    <t>malloc.o</t>
+  </si>
+  <si>
+    <t>depilogue.o</t>
   </si>
   <si>
     <t>fmodf.o</t>
@@ -239,121 +260,73 @@
     <t>arm_cos_f32.o</t>
   </si>
   <si>
+    <t>stm32g4xx_it.o</t>
+  </si>
+  <si>
     <t>arm_sin_f32.o</t>
   </si>
   <si>
+    <t>dev_config.o</t>
+  </si>
+  <si>
     <t>drv_adc.o</t>
   </si>
   <si>
-    <t>fnaninf.o</t>
-  </si>
-  <si>
-    <t>init_alloc.o</t>
-  </si>
-  <si>
     <t>list.o</t>
   </si>
   <si>
-    <t>stm32g4xx_it.o</t>
-  </si>
-  <si>
-    <t>dev_config.o</t>
-  </si>
-  <si>
-    <t>_printf_dec.o</t>
-  </si>
-  <si>
-    <t>sys_io.o</t>
-  </si>
-  <si>
     <t>drv_gpio.o</t>
   </si>
   <si>
     <t>floorf.o</t>
   </si>
   <si>
-    <t>__printf.o</t>
-  </si>
-  <si>
-    <t>rt_memcpy_w.o</t>
+    <t>fepilogue.o</t>
+  </si>
+  <si>
+    <t>uldiv.o</t>
+  </si>
+  <si>
+    <t>ldiv.o</t>
+  </si>
+  <si>
+    <t>motor_param.o</t>
+  </si>
+  <si>
+    <t>cmsis_os.o</t>
+  </si>
+  <si>
+    <t>assert_report.o</t>
+  </si>
+  <si>
+    <t>frem.o</t>
+  </si>
+  <si>
+    <t>dma.o</t>
   </si>
   <si>
     <t>frnd.o</t>
   </si>
   <si>
-    <t>motor_param.o</t>
-  </si>
-  <si>
-    <t>h1_alloc.o</t>
-  </si>
-  <si>
-    <t>cmsis_os.o</t>
-  </si>
-  <si>
-    <t>assert_report.o</t>
-  </si>
-  <si>
-    <t>_printf_str.o</t>
-  </si>
-  <si>
-    <t>defsig_rtmem_inner.o</t>
-  </si>
-  <si>
-    <t>rt_memclr_w.o</t>
-  </si>
-  <si>
-    <t>h1_free.o</t>
-  </si>
-  <si>
-    <t>fclose.o</t>
-  </si>
-  <si>
-    <t>dma.o</t>
-  </si>
-  <si>
-    <t>sys_stackheap_outer.o</t>
-  </si>
-  <si>
-    <t>llsdiv.o</t>
-  </si>
-  <si>
-    <t>setvbuf.o</t>
-  </si>
-  <si>
-    <t>ftell.o</t>
-  </si>
-  <si>
-    <t>strlen.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_msp.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_cordic.o</t>
   </si>
   <si>
-    <t>h1_extend.o</t>
-  </si>
-  <si>
-    <t>defsig_rtred_inner.o</t>
-  </si>
-  <si>
-    <t>__scatter.o</t>
-  </si>
-  <si>
     <t>control_irq.o</t>
   </si>
   <si>
-    <t>defsig_general.o</t>
-  </si>
-  <si>
-    <t>_printf_char_common.o</t>
+    <t>dfixul.o</t>
+  </si>
+  <si>
+    <t>cdrcmple.o</t>
   </si>
   <si>
     <t>drv_dwt_timer.o</t>
   </si>
   <si>
-    <t>_printf_char.o</t>
+    <t>uidiv.o</t>
   </si>
   <si>
     <t>user_interface.o</t>
@@ -365,7 +338,19 @@
     <t>fpclassifyf.o</t>
   </si>
   <si>
-    <t>_printf_char_file.o</t>
+    <t>memseta.o</t>
+  </si>
+  <si>
+    <t>memcpya.o</t>
+  </si>
+  <si>
+    <t>llsshr.o</t>
+  </si>
+  <si>
+    <t>init.o</t>
+  </si>
+  <si>
+    <t>llushr.o</t>
   </si>
   <si>
     <t>thread_idle.o</t>
@@ -374,7 +359,10 @@
     <t>thread_control.o</t>
   </si>
   <si>
-    <t>__scatter_zi.o</t>
+    <t>llshl.o</t>
+  </si>
+  <si>
+    <t>handlers.o</t>
   </si>
   <si>
     <t>thread_period.o</t>
@@ -383,94 +371,19 @@
     <t>thread_display.o</t>
   </si>
   <si>
-    <t>thread_commun.o</t>
-  </si>
-  <si>
-    <t>__scatter_copy.o</t>
-  </si>
-  <si>
-    <t>noretval__2printf.o</t>
-  </si>
-  <si>
-    <t>_rserrno.o</t>
-  </si>
-  <si>
-    <t>libinit2.o</t>
-  </si>
-  <si>
-    <t>exit.o</t>
-  </si>
-  <si>
-    <t>sys_wrch.o</t>
-  </si>
-  <si>
-    <t>h1_init.o</t>
-  </si>
-  <si>
-    <t>defsig_rtred_outer.o</t>
-  </si>
-  <si>
-    <t>defsig_rtmem_outer.o</t>
-  </si>
-  <si>
-    <t>sys_exit.o</t>
-  </si>
-  <si>
-    <t>__rtentry2.o</t>
-  </si>
-  <si>
-    <t>fpinit.o</t>
-  </si>
-  <si>
-    <t>rtexit2.o</t>
-  </si>
-  <si>
-    <t>defsig_exit.o</t>
-  </si>
-  <si>
-    <t>rt_errno_addr_intlibspace.o</t>
-  </si>
-  <si>
-    <t>ferror.o</t>
-  </si>
-  <si>
-    <t>__main.o</t>
-  </si>
-  <si>
-    <t>libshutdown2.o</t>
-  </si>
-  <si>
-    <t>heapauxi.o</t>
-  </si>
-  <si>
-    <t>_printf_s.o</t>
-  </si>
-  <si>
-    <t>_printf_d.o</t>
-  </si>
-  <si>
-    <t>__rtentry4.o</t>
-  </si>
-  <si>
-    <t>hguard.o</t>
-  </si>
-  <si>
-    <t>_printf_percent_end.o</t>
-  </si>
-  <si>
-    <t>use_no_semi.o</t>
-  </si>
-  <si>
-    <t>rtexit.o</t>
-  </si>
-  <si>
-    <t>libshutdown.o</t>
-  </si>
-  <si>
-    <t>libinit.o</t>
-  </si>
-  <si>
-    <t>drv_usart.o</t>
+    <t>strncpy.o</t>
+  </si>
+  <si>
+    <t>entry9a.o</t>
+  </si>
+  <si>
+    <t>entry2.o</t>
+  </si>
+  <si>
+    <t>entry5.o</t>
+  </si>
+  <si>
+    <t>entry12b.o</t>
   </si>
   <si>
     <t>File_name</t>
@@ -590,9 +503,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$153</c:f>
+              <c:f>ram_percent!$A$3:$A$124</c:f>
               <c:strCache>
-                <c:ptCount val="151"/>
+                <c:ptCount val="122"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -600,25 +513,25 @@
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>dev_commun_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
+                  <c:v>packer_parser.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>c_w.l</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>tasks.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>stdio_streams.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>tim.o</c:v>
@@ -639,10 +552,10 @@
                   <c:v>fdcan.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>libspace.o</c:v>
+                  <c:v>i2c.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>i2c.o</c:v>
+                  <c:v>drv_usart.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
@@ -657,24 +570,39 @@
                   <c:v>thread_management.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>mc_w.l</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
+                  <c:v>mvars.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
+                  <c:v>stdout.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>errno.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="30">
+                  <c:v>jm_proto_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="150">
+                <c:pt idx="121">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -682,92 +610,107 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$153</c:f>
+              <c:f>ram_percent!$B$3:$B$124</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="151"/>
+                <c:ptCount val="122"/>
                 <c:pt idx="0">
-                  <c:v>71.16660308837891</c:v>
+                  <c:v>65.29313659667969</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.213768482208252</c:v>
+                  <c:v>6.618407249450684</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.658863544464111</c:v>
+                  <c:v>6.538859367370606</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.976850032806397</c:v>
+                  <c:v>6.109299182891846</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.560671091079712</c:v>
+                  <c:v>4.1007080078125</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.543330311775208</c:v>
+                  <c:v>1.813698172569275</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.47396719455719</c:v>
+                  <c:v>1.41595733165741</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.300559282302856</c:v>
+                  <c:v>1.3523188829422</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.144492149353027</c:v>
+                  <c:v>1.193222522735596</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.9884250164031982</c:v>
+                  <c:v>0.9068490862846375</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9710842370986939</c:v>
+                  <c:v>0.890939474105835</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8670395016670227</c:v>
+                  <c:v>0.7954816818237305</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5549052953720093</c:v>
+                  <c:v>0.5091082453727722</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4682013392448425</c:v>
+                  <c:v>0.4295600950717926</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.4335197508335114</c:v>
+                  <c:v>0.3977408409118652</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.416178971529007</c:v>
+                  <c:v>0.3341023027896881</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.364156574010849</c:v>
+                  <c:v>0.3341023027896881</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.3294750154018402</c:v>
+                  <c:v>0.3022830188274384</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1734078973531723</c:v>
+                  <c:v>0.1590963304042816</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.09970954060554504</c:v>
+                  <c:v>0.09148038923740387</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.08670394867658615</c:v>
+                  <c:v>0.07954816520214081</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.05202237144112587</c:v>
+                  <c:v>0.06363853067159653</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.05202237144112587</c:v>
+                  <c:v>0.04772889986634255</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.03468158096075058</c:v>
+                  <c:v>0.04772889986634255</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.03468158096075058</c:v>
+                  <c:v>0.03181926533579826</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.01734079048037529</c:v>
+                  <c:v>0.03181926533579826</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.01734079048037529</c:v>
-                </c:pt>
-                <c:pt idx="150">
+                  <c:v>0.03181926533579826</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.01590963266789913</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.01590963266789913</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.01590963266789913</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.01590963266789913</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.01590963266789913</c:v>
+                </c:pt>
+                <c:pt idx="121">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -835,460 +778,373 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$153</c:f>
+              <c:f>flash_percent!$A$3:$A$124</c:f>
               <c:strCache>
-                <c:ptCount val="151"/>
+                <c:ptCount val="122"/>
                 <c:pt idx="0">
-                  <c:v>c_w.l</c:v>
+                  <c:v>stm32g4xx_hal_uart.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>stm32g4xx_hal_tim.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>mc_w.l</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>stm32g4xx_hal_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>stm32g4xx_hal_uart.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>arm_cortexM4lf_math.lib</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>printfa.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>stm32g4xx_hal_adc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>arm_common_tables.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>motion_param.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
+                  <c:v>jm_proto.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>stm32g4xx_hal_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
+                  <c:v>mf_w.l</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>dev_motor_phase_current.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="18">
                   <c:v>stm32g4xx_hal_fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="19">
+                  <c:v>stm32g4xx_hal_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>multiturn_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
-                  <c:v>stm32g4xx_hal_dma.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="24">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>cascade_control.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
+                  <c:v>dev_commun_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>dev_half_bridge.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="31">
+                  <c:v>crc16.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>heap_4.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
-                  <c:v>motor_loop.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>heap_4.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>fz_wm.l</c:v>
-                </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="35">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="37">
+                  <c:v>packer_parser.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>drv_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="40">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="41">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="42">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="43">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="44">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="45">
+                  <c:v>dadd.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="47">
                   <c:v>ctrl_transition.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
-                  <c:v>initio.o</c:v>
-                </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="48">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="49">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="50">
+                  <c:v>jm_proto_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="51">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="52">
+                  <c:v>thread_commun.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
-                  <c:v>fseek.o</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>frem_clz.o</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>stdio.o</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>lludivv7m.o</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>fopen.o</c:v>
-                </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="54">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="55">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>ddiv.o</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="58">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="59">
                   <c:v>drv_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="60">
                   <c:v>stm32g4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="61">
+                  <c:v>malloc.o</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
-                  <c:v>_printf_intcommon.o</c:v>
-                </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="63">
+                  <c:v>depilogue.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>fmodf.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="65">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="66">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="67">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="68">
                   <c:v>roundf.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="69">
                   <c:v>arm_cos_f32.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>arm_sin_f32.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>drv_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>fnaninf.o</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>init_alloc.o</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>list.o</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>stm32g4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="71">
+                  <c:v>arm_sin_f32.o</c:v>
+                </c:pt>
+                <c:pt idx="72">
                   <c:v>dev_config.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
-                  <c:v>_printf_dec.o</c:v>
-                </c:pt>
                 <c:pt idx="73">
+                  <c:v>drv_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>list.o</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
+                </c:pt>
+                <c:pt idx="76">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
-                  <c:v>sys_io.o</c:v>
-                </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="77">
                   <c:v>drv_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="78">
                   <c:v>floorf.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
-                  <c:v>__printf.o</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>rt_memcpy_w.o</c:v>
-                </c:pt>
                 <c:pt idx="79">
+                  <c:v>fepilogue.o</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>uldiv.o</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>ldiv.o</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>motor_param.o</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>cmsis_os.o</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>assert_report.o</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>app_freertos.o</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>frem.o</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>cordic.o</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>stm32g4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>frnd.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
-                  <c:v>motor_param.o</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>h1_alloc.o</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>cmsis_os.o</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>assert_report.o</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>app_freertos.o</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>_printf_str.o</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>defsig_rtmem_inner.o</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>rt_memclr_w.o</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>h1_free.o</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>fclose.o</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>dma.o</c:v>
-                </c:pt>
                 <c:pt idx="91">
-                  <c:v>cordic.o</c:v>
+                  <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>sys_stackheap_outer.o</c:v>
+                  <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>llsdiv.o</c:v>
+                  <c:v>control_irq.o</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>setvbuf.o</c:v>
+                  <c:v>dfixul.o</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>stm32g4xx_hal.o</c:v>
+                  <c:v>cdrcmple.o</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>ftell.o</c:v>
+                  <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>strlen.o</c:v>
+                  <c:v>uidiv.o</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>stm32g4xx_hal_msp.o</c:v>
+                  <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>stm32g4xx_hal_cordic.o</c:v>
+                  <c:v>user_interface.o</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>h1_extend.o</c:v>
+                  <c:v>funder.o</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>defsig_rtred_inner.o</c:v>
+                  <c:v>fpclassifyf.o</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>__scatter.o</c:v>
+                  <c:v>memseta.o</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>control_irq.o</c:v>
+                  <c:v>memcpya.o</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>defsig_general.o</c:v>
+                  <c:v>llsshr.o</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>_printf_char_common.o</c:v>
+                  <c:v>init.o</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>drv_dwt_timer.o</c:v>
+                  <c:v>llushr.o</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>_printf_char.o</c:v>
+                  <c:v>thread_idle.o</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>system_stm32g4xx.o</c:v>
+                  <c:v>thread_control.o</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>user_interface.o</c:v>
+                  <c:v>llshl.o</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>funder.o</c:v>
+                  <c:v>handlers.o</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>fpclassifyf.o</c:v>
+                  <c:v>thread_period.o</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>_printf_char_file.o</c:v>
+                  <c:v>thread_display.o</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>thread_idle.o</c:v>
+                  <c:v>strncpy.o</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>thread_control.o</c:v>
+                  <c:v>errno.o</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>__scatter_zi.o</c:v>
+                  <c:v>mvars.o</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>thread_period.o</c:v>
+                  <c:v>entry9a.o</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>thread_display.o</c:v>
+                  <c:v>entry2.o</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>thread_commun.o</c:v>
+                  <c:v>stdout.o</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>__scatter_copy.o</c:v>
+                  <c:v>entry5.o</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>noretval__2printf.o</c:v>
+                  <c:v>entry12b.o</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>_rserrno.o</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>libinit2.o</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>exit.o</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>sys_wrch.o</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>h1_init.o</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>defsig_rtred_outer.o</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>defsig_rtmem_outer.o</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>sys_exit.o</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>stdio_streams.o</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>__rtentry2.o</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>fpinit.o</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>rtexit2.o</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>defsig_exit.o</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>rt_errno_addr_intlibspace.o</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>libspace.o</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>ferror.o</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>__main.o</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>libshutdown2.o</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>heapauxi.o</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>_printf_s.o</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>_printf_d.o</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>__rtentry4.o</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>hguard.o</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>_printf_percent_end.o</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>use_no_semi.o</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>rtexit.o</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>libshutdown.o</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>libinit.o</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>drv_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="150">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1296,461 +1152,374 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$153</c:f>
+              <c:f>flash_percent!$B$3:$B$124</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="151"/>
+                <c:ptCount val="122"/>
                 <c:pt idx="0">
-                  <c:v>6.487202167510986</c:v>
+                  <c:v>5.55370569229126</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.865695953369141</c:v>
+                  <c:v>5.310647964477539</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.11179780960083</c:v>
+                  <c:v>4.924418926239014</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.379964828491211</c:v>
+                  <c:v>4.628087997436523</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.317446231842041</c:v>
+                  <c:v>3.908903360366821</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.037952423095703</c:v>
+                  <c:v>3.692481756210327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.773168563842773</c:v>
+                  <c:v>3.655856609344482</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.493674516677856</c:v>
+                  <c:v>3.416128396987915</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.320829629898071</c:v>
+                  <c:v>3.163081884384155</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.765519380569458</c:v>
+                  <c:v>3.006592512130737</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.563253879547119</c:v>
+                  <c:v>2.503829002380371</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.372021198272705</c:v>
+                  <c:v>2.327362298965454</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.210208892822266</c:v>
+                  <c:v>2.320703268051148</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.177110910415649</c:v>
+                  <c:v>2.194180011749268</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.982200622558594</c:v>
+                  <c:v>2.147566080093384</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.813033223152161</c:v>
+                  <c:v>2.001065492630005</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.529861688613892</c:v>
+                  <c:v>1.971099376678467</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.452633142471314</c:v>
+                  <c:v>1.794632792472839</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.441600441932678</c:v>
+                  <c:v>1.641473054885864</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.390114784240723</c:v>
+                  <c:v>1.591529607772827</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.3643718957901</c:v>
+                  <c:v>1.385096907615662</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.32391881942749</c:v>
+                  <c:v>1.315176129341126</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.312886118888855</c:v>
+                  <c:v>1.305187463760376</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.287143230438232</c:v>
+                  <c:v>1.258573651313782</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.217269778251648</c:v>
+                  <c:v>1.198641538619995</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.202559590339661</c:v>
+                  <c:v>1.188652873039246</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.147396326065064</c:v>
+                  <c:v>1.165345907211304</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.985584020614624</c:v>
+                  <c:v>1.102084279060364</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.948808491230011</c:v>
+                  <c:v>1.088766098022461</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.9414533972740173</c:v>
+                  <c:v>1.065459132194519</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.9010003209114075</c:v>
+                  <c:v>1.038822650909424</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.8476758003234863</c:v>
+                  <c:v>0.9256176352500916</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.8311268091201782</c:v>
+                  <c:v>0.8590264320373535</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.8090614676475525</c:v>
+                  <c:v>0.8523673415184021</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.7538982033729553</c:v>
+                  <c:v>0.8457081913948059</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.7355104684829712</c:v>
+                  <c:v>0.7674635648727417</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.6840246915817261</c:v>
+                  <c:v>0.7524805068969727</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.6729920506477356</c:v>
+                  <c:v>0.7524805068969727</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.6325389742851257</c:v>
+                  <c:v>0.7358327507972717</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.6104736924171448</c:v>
+                  <c:v>0.7325031757354736</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.5847308039665222</c:v>
+                  <c:v>0.6825597882270813</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.5736981630325317</c:v>
+                  <c:v>0.6659119725227356</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.5663430690765381</c:v>
+                  <c:v>0.6192981004714966</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.5111797451972961</c:v>
+                  <c:v>0.6093094348907471</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.5001471042633057</c:v>
+                  <c:v>0.5726842880249023</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.4633715748786926</c:v>
+                  <c:v>0.5560364723205566</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.456016480922699</c:v>
+                  <c:v>0.5527069568634033</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.4486613571643829</c:v>
+                  <c:v>0.5293999910354614</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.4413062632083893</c:v>
+                  <c:v>0.5127522349357605</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.4376287162303925</c:v>
+                  <c:v>0.4628088176250458</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.4339511692523956</c:v>
+                  <c:v>0.4528201520442963</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.4302736222743988</c:v>
+                  <c:v>0.4528201520442963</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.4045307338237763</c:v>
+                  <c:v>0.4195245504379273</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.4045307338237763</c:v>
+                  <c:v>0.4195245504379273</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.4045307338237763</c:v>
+                  <c:v>0.3895584940910339</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.3751103281974793</c:v>
+                  <c:v>0.3795698285102844</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.3456899225711823</c:v>
+                  <c:v>0.3695811331272125</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.3273021578788757</c:v>
+                  <c:v>0.3662515878677368</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.3236245810985565</c:v>
+                  <c:v>0.3662515878677368</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.3236245810985565</c:v>
+                  <c:v>0.3662515878677368</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.2942041754722595</c:v>
+                  <c:v>0.3396151065826416</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.2905266284942627</c:v>
+                  <c:v>0.3129786252975464</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.283171534538269</c:v>
+                  <c:v>0.3129786252975464</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.2794939577579498</c:v>
+                  <c:v>0.3096490502357483</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.2647837698459625</c:v>
+                  <c:v>0.293001264333725</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.2611061930656433</c:v>
+                  <c:v>0.293001264333725</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.2574286460876465</c:v>
+                  <c:v>0.2663647830486298</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.2537510991096497</c:v>
+                  <c:v>0.2630352377891541</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.2537510991096497</c:v>
+                  <c:v>0.2563761174678803</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.2500735521316528</c:v>
+                  <c:v>0.2530465424060822</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.242718443274498</c:v>
+                  <c:v>0.2463874220848084</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.2224919050931931</c:v>
+                  <c:v>0.2397283017635346</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.2206531316041946</c:v>
+                  <c:v>0.2380635291337967</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.2206531316041946</c:v>
+                  <c:v>0.2363987416028976</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.209620475769043</c:v>
+                  <c:v>0.2297396212816238</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.209620475769043</c:v>
+                  <c:v>0.2264100760221481</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.2059429287910461</c:v>
+                  <c:v>0.1997735947370529</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.1912327110767365</c:v>
+                  <c:v>0.1897849142551422</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.1838776171207428</c:v>
+                  <c:v>0.1864553540945053</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.176522508263588</c:v>
+                  <c:v>0.1831257939338684</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.176522508263588</c:v>
+                  <c:v>0.163148432970047</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.1728449612855911</c:v>
+                  <c:v>0.163148432970047</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.1544571965932846</c:v>
+                  <c:v>0.1598188728094101</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.1544571965932846</c:v>
+                  <c:v>0.1398415118455887</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.1544571965932846</c:v>
+                  <c:v>0.1398415118455887</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.1507796347141266</c:v>
+                  <c:v>0.1398415118455887</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.1471020877361298</c:v>
+                  <c:v>0.1365119516849518</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.1434245407581329</c:v>
+                  <c:v>0.1265232712030411</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.1434245407581329</c:v>
+                  <c:v>0.1265232712030411</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.1397469788789749</c:v>
+                  <c:v>0.1165345907211304</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.1397469788789749</c:v>
+                  <c:v>0.09988679736852646</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.1397469788789749</c:v>
+                  <c:v>0.09988679736852646</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.1360694319009781</c:v>
+                  <c:v>0.08989811688661575</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.1323918849229813</c:v>
+                  <c:v>0.08656855672597885</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1287143230438232</c:v>
+                  <c:v>0.07990943640470505</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1287143230438232</c:v>
+                  <c:v>0.07990943640470505</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.121359221637249</c:v>
+                  <c:v>0.07990943640470505</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1140041202306747</c:v>
+                  <c:v>0.07325031608343124</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1103265658020973</c:v>
+                  <c:v>0.07325031608343124</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.09929390996694565</c:v>
+                  <c:v>0.06992075592279434</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.09561635553836823</c:v>
+                  <c:v>0.06326163560152054</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.09561635553836823</c:v>
+                  <c:v>0.06326163560152054</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.09561635553836823</c:v>
+                  <c:v>0.05993207544088364</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.09561635553836823</c:v>
+                  <c:v>0.05993207544088364</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.0919388085603714</c:v>
+                  <c:v>0.05993207544088364</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.08826125413179398</c:v>
+                  <c:v>0.05993207544088364</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.08826125413179398</c:v>
+                  <c:v>0.05327295884490013</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.08090614527463913</c:v>
+                  <c:v>0.05327295884490013</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.08090614527463913</c:v>
+                  <c:v>0.05327295884490013</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.0772285982966423</c:v>
+                  <c:v>0.04994339868426323</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.06987348943948746</c:v>
+                  <c:v>0.04994339868426323</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.06987348943948746</c:v>
+                  <c:v>0.04661383852362633</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.06619594246149063</c:v>
+                  <c:v>0.04661383852362633</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.05884083732962608</c:v>
+                  <c:v>0.03995471820235252</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.05884083732962608</c:v>
+                  <c:v>0.02663647942245007</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.05148573219776154</c:v>
+                  <c:v>0.01331823971122503</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.05148573219776154</c:v>
+                  <c:v>0.01331823971122503</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.05148573219776154</c:v>
+                  <c:v>0.01331823971122503</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.05148573219776154</c:v>
+                  <c:v>0.006659119855612516</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.04780817776918411</c:v>
+                  <c:v>0.006659119855612516</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.04413062706589699</c:v>
+                  <c:v>0.006659119855612516</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.04045307263731957</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>0.03309797123074532</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>0.03309797123074532</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>0.02574286609888077</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>0.02574286609888077</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>0.02574286609888077</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>0.02574286609888077</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>0.02206531353294849</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>0.02206531353294849</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>0.02206531353294849</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>0.01838776096701622</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>0.01838776096701622</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>0.01838776096701622</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>0.01471020933240652</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>0.01471020933240652</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>0.01471020933240652</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>0.01471020933240652</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>0.01103265676647425</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>0.01103265676647425</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>0.01103265676647425</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>0.01103265676647425</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>0.01103265676647425</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>0.00735510466620326</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>0.00735510466620326</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>0.00367755233310163</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>0.00367755233310163</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>0.00367755233310163</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>0.00367755233310163</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>0.00367755233310163</c:v>
-                </c:pt>
-                <c:pt idx="150">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1855,8 +1624,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H153" totalsRowCount="1">
-  <autoFilter ref="A2:H152"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H124" totalsRowCount="1">
+  <autoFilter ref="A2:H123"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1872,8 +1641,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H153" totalsRowCount="1">
-  <autoFilter ref="A2:H152"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H124" totalsRowCount="1">
+  <autoFilter ref="A2:H123"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2173,7 +1942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2186,28 +1955,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="F2" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="H2" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2215,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>71.16660308837891</v>
+        <v>65.29313659667969</v>
       </c>
       <c r="C3" s="1">
         <v>16416</v>
@@ -2241,7 +2010,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>7.213768482208252</v>
+        <v>6.618407249450684</v>
       </c>
       <c r="C4" s="1">
         <v>1664</v>
@@ -2267,25 +2036,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>6.658863544464111</v>
+        <v>6.538859367370606</v>
       </c>
       <c r="C5" s="1">
-        <v>1536</v>
+        <v>1644</v>
       </c>
       <c r="D5" s="1">
-        <v>536</v>
+        <v>640</v>
       </c>
       <c r="E5" s="1">
-        <v>64</v>
+        <v>636</v>
       </c>
       <c r="F5" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="1">
-        <v>1536</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2293,25 +2062,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.976850032806397</v>
+        <v>6.109299182891846</v>
       </c>
       <c r="C6" s="1">
-        <v>456</v>
+        <v>1536</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>456</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2319,25 +2088,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>1.560671091079712</v>
+        <v>4.1007080078125</v>
       </c>
       <c r="C7" s="1">
-        <v>360</v>
+        <v>1031</v>
       </c>
       <c r="D7" s="1">
-        <v>3528</v>
+        <v>452</v>
       </c>
       <c r="E7" s="1">
-        <v>3504</v>
+        <v>452</v>
       </c>
       <c r="F7" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>348</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2345,25 +2114,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>1.543330311775208</v>
+        <v>1.813698172569275</v>
       </c>
       <c r="C8" s="1">
-        <v>356</v>
+        <v>456</v>
       </c>
       <c r="D8" s="1">
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>352</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2371,25 +2140,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1.47396719455719</v>
+        <v>1.41595733165741</v>
       </c>
       <c r="C9" s="1">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="D9" s="1">
-        <v>344</v>
+        <v>790</v>
       </c>
       <c r="E9" s="1">
-        <v>344</v>
+        <v>434</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>340</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2397,25 +2166,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>1.300559282302856</v>
+        <v>1.3523188829422</v>
       </c>
       <c r="C10" s="1">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="D10" s="1">
-        <v>1504</v>
+        <v>344</v>
       </c>
       <c r="E10" s="1">
-        <v>1444</v>
+        <v>344</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>240</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2423,25 +2192,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.144492149353027</v>
+        <v>1.193222522735596</v>
       </c>
       <c r="C11" s="1">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="D11" s="1">
-        <v>12</v>
+        <v>1504</v>
       </c>
       <c r="E11" s="1">
-        <v>0</v>
+        <v>1444</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2449,7 +2218,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.9884250164031982</v>
+        <v>0.9068490862846375</v>
       </c>
       <c r="C12" s="1">
         <v>228</v>
@@ -2475,7 +2244,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.9710842370986939</v>
+        <v>0.890939474105835</v>
       </c>
       <c r="C13" s="1">
         <v>224</v>
@@ -2501,7 +2270,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.8670395016670227</v>
+        <v>0.7954816818237305</v>
       </c>
       <c r="C14" s="1">
         <v>200</v>
@@ -2527,7 +2296,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.5549052953720093</v>
+        <v>0.5091082453727722</v>
       </c>
       <c r="C15" s="1">
         <v>128</v>
@@ -2553,7 +2322,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.4682013392448425</v>
+        <v>0.4295600950717926</v>
       </c>
       <c r="C16" s="1">
         <v>108</v>
@@ -2579,7 +2348,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.4335197508335114</v>
+        <v>0.3977408409118652</v>
       </c>
       <c r="C17" s="1">
         <v>100</v>
@@ -2605,16 +2374,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.416178971529007</v>
+        <v>0.3341023027896881</v>
       </c>
       <c r="C18" s="1">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D18" s="1">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="E18" s="1">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2623,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2631,19 +2400,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.364156574010849</v>
+        <v>0.3341023027896881</v>
       </c>
       <c r="C19" s="1">
         <v>84</v>
       </c>
       <c r="D19" s="1">
-        <v>252</v>
+        <v>442</v>
       </c>
       <c r="E19" s="1">
-        <v>252</v>
+        <v>386</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -2657,7 +2426,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.3294750154018402</v>
+        <v>0.3022830188274384</v>
       </c>
       <c r="C20" s="1">
         <v>76</v>
@@ -2683,7 +2452,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.1734078973531723</v>
+        <v>0.1590963304042816</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -2709,7 +2478,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.09970954060554504</v>
+        <v>0.09148038923740387</v>
       </c>
       <c r="C22" s="1">
         <v>23</v>
@@ -2735,7 +2504,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.08670394867658615</v>
+        <v>0.07954816520214081</v>
       </c>
       <c r="C23" s="1">
         <v>20</v>
@@ -2761,22 +2530,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.05202237144112587</v>
+        <v>0.06363853067159653</v>
       </c>
       <c r="C24" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1">
-        <v>70</v>
+        <v>2958</v>
       </c>
       <c r="E24" s="1">
-        <v>58</v>
+        <v>2942</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -2787,16 +2556,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.05202237144112587</v>
+        <v>0.04772889986634255</v>
       </c>
       <c r="C25" s="1">
         <v>12</v>
       </c>
       <c r="D25" s="1">
-        <v>714</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1">
-        <v>702</v>
+        <v>58</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2813,22 +2582,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.03468158096075058</v>
+        <v>0.04772889986634255</v>
       </c>
       <c r="C26" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="1">
-        <v>1202</v>
+        <v>714</v>
       </c>
       <c r="E26" s="1">
-        <v>1014</v>
+        <v>702</v>
       </c>
       <c r="F26" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -2839,16 +2608,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.03468158096075058</v>
+        <v>0.03181926533579826</v>
       </c>
       <c r="C27" s="1">
         <v>8</v>
       </c>
       <c r="D27" s="1">
-        <v>1078</v>
+        <v>8</v>
       </c>
       <c r="E27" s="1">
-        <v>1070</v>
+        <v>0</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2865,22 +2634,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.01734079048037529</v>
+        <v>0.03181926533579826</v>
       </c>
       <c r="C28" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1">
-        <v>44</v>
+        <v>1202</v>
       </c>
       <c r="E28" s="1">
-        <v>16</v>
+        <v>1014</v>
       </c>
       <c r="F28" s="1">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="G28" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -2891,56 +2660,186 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.01734079048037529</v>
+        <v>0.03181926533579826</v>
       </c>
       <c r="C29" s="1">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1078</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1070</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>8</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.01590963266789913</v>
+      </c>
+      <c r="C30" s="1">
         <v>4</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D30" s="1">
+        <v>4</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.01590963266789913</v>
+      </c>
+      <c r="C31" s="1">
+        <v>4</v>
+      </c>
+      <c r="D31" s="1">
+        <v>16</v>
+      </c>
+      <c r="E31" s="1">
+        <v>12</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.01590963266789913</v>
+      </c>
+      <c r="C32" s="1">
+        <v>4</v>
+      </c>
+      <c r="D32" s="1">
+        <v>44</v>
+      </c>
+      <c r="E32" s="1">
+        <v>16</v>
+      </c>
+      <c r="F32" s="1">
+        <v>24</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.01590963266789913</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4</v>
+      </c>
+      <c r="D33" s="1">
+        <v>272</v>
+      </c>
+      <c r="E33" s="1">
+        <v>268</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>4</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.01590963266789913</v>
+      </c>
+      <c r="C34" s="1">
+        <v>4</v>
+      </c>
+      <c r="D34" s="1">
         <v>84</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E34" s="1">
         <v>48</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F34" s="1">
         <v>32</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G34" s="1">
         <v>4</v>
       </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
-      <c r="A153" t="s">
-        <v>153</v>
-      </c>
-      <c r="B153">
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+      <c r="B124">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C153">
+      <c r="C124">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D153">
+      <c r="D124">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E153">
+      <c r="E124">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F153">
+      <c r="F124">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G153">
+      <c r="G124">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H153">
+      <c r="H124">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2956,7 +2855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2969,62 +2868,62 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="F2" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="H2" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2">
-        <v>6.487202167510986</v>
+        <v>5.55370569229126</v>
       </c>
       <c r="C3" s="1">
-        <v>3528</v>
+        <v>3336</v>
       </c>
       <c r="D3" s="1">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>3504</v>
+        <v>3312</v>
       </c>
       <c r="F3" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2">
-        <v>5.865695953369141</v>
+        <v>5.310647964477539</v>
       </c>
       <c r="C4" s="1">
         <v>3190</v>
@@ -3047,25 +2946,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>5.11179780960083</v>
+        <v>4.924418926239014</v>
       </c>
       <c r="C5" s="1">
-        <v>2780</v>
+        <v>2958</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1">
-        <v>2780</v>
+        <v>2942</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -3073,22 +2972,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2">
-        <v>4.379964828491211</v>
+        <v>4.628087997436523</v>
       </c>
       <c r="C6" s="1">
-        <v>2382</v>
+        <v>2780</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>2358</v>
+        <v>2780</v>
       </c>
       <c r="F6" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -3099,10 +2998,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2">
-        <v>4.317446231842041</v>
+        <v>3.908903360366821</v>
       </c>
       <c r="C7" s="1">
         <v>2348</v>
@@ -3125,19 +3024,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2">
-        <v>4.037952423095703</v>
+        <v>3.692481756210327</v>
       </c>
       <c r="C8" s="1">
-        <v>2196</v>
+        <v>2218</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2196</v>
+        <v>2218</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -3151,22 +3050,22 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2">
-        <v>3.773168563842773</v>
+        <v>3.655856609344482</v>
       </c>
       <c r="C9" s="1">
-        <v>2052</v>
+        <v>2196</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>2196</v>
       </c>
       <c r="F9" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -3177,22 +3076,22 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2">
-        <v>3.493674516677856</v>
+        <v>3.416128396987915</v>
       </c>
       <c r="C10" s="1">
-        <v>1900</v>
+        <v>2052</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -3203,19 +3102,19 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2">
-        <v>3.320829629898071</v>
+        <v>3.163081884384155</v>
       </c>
       <c r="C11" s="1">
-        <v>1806</v>
+        <v>1900</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>1806</v>
+        <v>1900</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -3229,74 +3128,74 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2">
-        <v>2.765519380569458</v>
+        <v>3.006592512130737</v>
       </c>
       <c r="C12" s="1">
-        <v>1504</v>
+        <v>1806</v>
       </c>
       <c r="D12" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1444</v>
+        <v>1806</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2">
-        <v>2.563253879547119</v>
+        <v>2.503829002380371</v>
       </c>
       <c r="C13" s="1">
-        <v>1394</v>
+        <v>1504</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E13" s="1">
-        <v>1394</v>
+        <v>1444</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2">
-        <v>2.372021198272705</v>
+        <v>2.327362298965454</v>
       </c>
       <c r="C14" s="1">
-        <v>1290</v>
+        <v>1398</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1258</v>
+        <v>1398</v>
       </c>
       <c r="F14" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -3307,25 +3206,25 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2">
-        <v>2.210208892822266</v>
+        <v>2.320703268051148</v>
       </c>
       <c r="C15" s="1">
-        <v>1202</v>
+        <v>1394</v>
       </c>
       <c r="D15" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1014</v>
+        <v>1394</v>
       </c>
       <c r="F15" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -3333,19 +3232,19 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2">
-        <v>2.177110910415649</v>
+        <v>2.194180011749268</v>
       </c>
       <c r="C16" s="1">
-        <v>1184</v>
+        <v>1318</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>1184</v>
+        <v>1318</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -3359,25 +3258,25 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2">
-        <v>1.982200622558594</v>
+        <v>2.147566080093384</v>
       </c>
       <c r="C17" s="1">
-        <v>1078</v>
+        <v>1290</v>
       </c>
       <c r="D17" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>1070</v>
+        <v>1258</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G17" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -3385,25 +3284,25 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2">
-        <v>1.813033223152161</v>
+        <v>2.001065492630005</v>
       </c>
       <c r="C18" s="1">
-        <v>986</v>
+        <v>1202</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1">
-        <v>986</v>
+        <v>1014</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -3411,19 +3310,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B19" s="2">
-        <v>1.529861688613892</v>
+        <v>1.971099376678467</v>
       </c>
       <c r="C19" s="1">
-        <v>832</v>
+        <v>1184</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>832</v>
+        <v>1184</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -3437,45 +3336,45 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
-        <v>1.452633142471314</v>
+        <v>1.794632792472839</v>
       </c>
       <c r="C20" s="1">
-        <v>790</v>
+        <v>1078</v>
       </c>
       <c r="D20" s="1">
-        <v>356</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1">
-        <v>434</v>
+        <v>1070</v>
       </c>
       <c r="F20" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H20" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B21" s="2">
-        <v>1.441600441932678</v>
+        <v>1.641473054885864</v>
       </c>
       <c r="C21" s="1">
-        <v>784</v>
+        <v>986</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>784</v>
+        <v>986</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -3489,19 +3388,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2">
-        <v>1.390114784240723</v>
+        <v>1.591529607772827</v>
       </c>
       <c r="C22" s="1">
-        <v>756</v>
+        <v>956</v>
       </c>
       <c r="D22" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>756</v>
+        <v>956</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -3510,24 +3409,24 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2">
-        <v>1.3643718957901</v>
+        <v>1.385096907615662</v>
       </c>
       <c r="C23" s="1">
-        <v>742</v>
+        <v>832</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>742</v>
+        <v>832</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -3541,51 +3440,51 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2">
-        <v>1.32391881942749</v>
+        <v>1.315176129341126</v>
       </c>
       <c r="C24" s="1">
-        <v>720</v>
+        <v>790</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E24" s="1">
-        <v>720</v>
+        <v>434</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2">
-        <v>1.312886118888855</v>
+        <v>1.305187463760376</v>
       </c>
       <c r="C25" s="1">
-        <v>714</v>
+        <v>784</v>
       </c>
       <c r="D25" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>702</v>
+        <v>784</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -3593,19 +3492,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B26" s="2">
-        <v>1.287143230438232</v>
+        <v>1.258573651313782</v>
       </c>
       <c r="C26" s="1">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E26" s="1">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -3614,24 +3513,24 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2">
-        <v>1.217269778251648</v>
+        <v>1.198641538619995</v>
       </c>
       <c r="C27" s="1">
-        <v>662</v>
+        <v>720</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>662</v>
+        <v>720</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -3645,25 +3544,25 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1.202559590339661</v>
+        <v>1.188652873039246</v>
       </c>
       <c r="C28" s="1">
-        <v>654</v>
+        <v>714</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E28" s="1">
-        <v>318</v>
+        <v>702</v>
       </c>
       <c r="F28" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -3671,19 +3570,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2">
-        <v>1.147396326065064</v>
+        <v>1.165345907211304</v>
       </c>
       <c r="C29" s="1">
-        <v>624</v>
+        <v>700</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>624</v>
+        <v>700</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -3697,97 +3596,97 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B30" s="2">
-        <v>0.985584020614624</v>
+        <v>1.102084279060364</v>
       </c>
       <c r="C30" s="1">
-        <v>536</v>
+        <v>662</v>
       </c>
       <c r="D30" s="1">
-        <v>1536</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="F30" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>1536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="B31" s="2">
-        <v>0.948808491230011</v>
+        <v>1.088766098022461</v>
       </c>
       <c r="C31" s="1">
-        <v>516</v>
+        <v>654</v>
       </c>
       <c r="D31" s="1">
-        <v>1664</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>516</v>
+        <v>318</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>1664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B32" s="2">
-        <v>0.9414533972740173</v>
+        <v>1.065459132194519</v>
       </c>
       <c r="C32" s="1">
-        <v>512</v>
+        <v>640</v>
       </c>
       <c r="D32" s="1">
-        <v>16416</v>
+        <v>1644</v>
       </c>
       <c r="E32" s="1">
-        <v>480</v>
+        <v>636</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H32" s="1">
-        <v>16384</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B33" s="2">
-        <v>0.9010003209114075</v>
+        <v>1.038822650909424</v>
       </c>
       <c r="C33" s="1">
-        <v>490</v>
+        <v>624</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>490</v>
+        <v>624</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -3801,25 +3700,25 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B34" s="2">
-        <v>0.8476758003234863</v>
+        <v>0.9256176352500916</v>
       </c>
       <c r="C34" s="1">
-        <v>461</v>
+        <v>556</v>
       </c>
       <c r="D34" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>426</v>
+        <v>44</v>
       </c>
       <c r="F34" s="1">
-        <v>12</v>
+        <v>512</v>
       </c>
       <c r="G34" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -3827,19 +3726,19 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B35" s="2">
-        <v>0.8311268091201782</v>
+        <v>0.8590264320373535</v>
       </c>
       <c r="C35" s="1">
-        <v>452</v>
+        <v>516</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>1664</v>
       </c>
       <c r="E35" s="1">
-        <v>452</v>
+        <v>516</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -3848,82 +3747,82 @@
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>0.8090614676475525</v>
+        <v>0.8523673415184021</v>
       </c>
       <c r="C36" s="1">
-        <v>440</v>
+        <v>512</v>
       </c>
       <c r="D36" s="1">
-        <v>108</v>
+        <v>16416</v>
       </c>
       <c r="E36" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H36" s="1">
-        <v>108</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>0.7538982033729553</v>
+        <v>0.8457081913948059</v>
       </c>
       <c r="C37" s="1">
-        <v>410</v>
+        <v>508</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="E37" s="1">
-        <v>330</v>
+        <v>36</v>
       </c>
       <c r="F37" s="1">
-        <v>80</v>
+        <v>472</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="B38" s="2">
-        <v>0.7355104684829712</v>
+        <v>0.7674635648727417</v>
       </c>
       <c r="C38" s="1">
-        <v>400</v>
+        <v>461</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -3931,22 +3830,22 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B39" s="2">
-        <v>0.6840246915817261</v>
+        <v>0.7524805068969727</v>
       </c>
       <c r="C39" s="1">
-        <v>372</v>
+        <v>452</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>340</v>
+        <v>452</v>
       </c>
       <c r="F39" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
@@ -3957,19 +3856,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="B40" s="2">
-        <v>0.6729920506477356</v>
+        <v>0.7524805068969727</v>
       </c>
       <c r="C40" s="1">
-        <v>366</v>
+        <v>452</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="E40" s="1">
-        <v>366</v>
+        <v>452</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3978,50 +3877,50 @@
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B41" s="2">
-        <v>0.6325389742851257</v>
+        <v>0.7358327507972717</v>
       </c>
       <c r="C41" s="1">
-        <v>344</v>
+        <v>442</v>
       </c>
       <c r="D41" s="1">
-        <v>340</v>
+        <v>84</v>
       </c>
       <c r="E41" s="1">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="F41" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>340</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B42" s="2">
-        <v>0.6104736924171448</v>
+        <v>0.7325031757354736</v>
       </c>
       <c r="C42" s="1">
-        <v>332</v>
+        <v>440</v>
       </c>
       <c r="D42" s="1">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="E42" s="1">
-        <v>332</v>
+        <v>440</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -4030,27 +3929,27 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>200</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B43" s="2">
-        <v>0.5847308039665222</v>
+        <v>0.6825597882270813</v>
       </c>
       <c r="C43" s="1">
-        <v>318</v>
+        <v>410</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
@@ -4061,19 +3960,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B44" s="2">
-        <v>0.5736981630325317</v>
+        <v>0.6659119725227356</v>
       </c>
       <c r="C44" s="1">
-        <v>312</v>
+        <v>400</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>312</v>
+        <v>400</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -4087,22 +3986,22 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B45" s="2">
-        <v>0.5663430690765381</v>
+        <v>0.6192981004714966</v>
       </c>
       <c r="C45" s="1">
-        <v>308</v>
+        <v>372</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="F45" s="1">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -4113,19 +4012,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B46" s="2">
-        <v>0.5111797451972961</v>
+        <v>0.6093094348907471</v>
       </c>
       <c r="C46" s="1">
-        <v>278</v>
+        <v>366</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>278</v>
+        <v>366</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -4139,19 +4038,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="B47" s="2">
-        <v>0.5001471042633057</v>
+        <v>0.5726842880249023</v>
       </c>
       <c r="C47" s="1">
-        <v>272</v>
+        <v>344</v>
       </c>
       <c r="D47" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E47" s="1">
-        <v>272</v>
+        <v>344</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -4160,24 +4059,24 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="B48" s="2">
-        <v>0.4633715748786926</v>
+        <v>0.5560364723205566</v>
       </c>
       <c r="C48" s="1">
-        <v>252</v>
+        <v>334</v>
       </c>
       <c r="D48" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>252</v>
+        <v>334</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -4186,24 +4085,24 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="B49" s="2">
-        <v>0.456016480922699</v>
+        <v>0.5527069568634033</v>
       </c>
       <c r="C49" s="1">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E49" s="1">
-        <v>248</v>
+        <v>332</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -4212,24 +4111,24 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B50" s="2">
-        <v>0.4486613571643829</v>
+        <v>0.5293999910354614</v>
       </c>
       <c r="C50" s="1">
-        <v>244</v>
+        <v>318</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>244</v>
+        <v>318</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -4243,22 +4142,22 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B51" s="2">
-        <v>0.4413062632083893</v>
+        <v>0.5127522349357605</v>
       </c>
       <c r="C51" s="1">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
@@ -4269,19 +4168,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B52" s="2">
-        <v>0.4376287162303925</v>
+        <v>0.4628088176250458</v>
       </c>
       <c r="C52" s="1">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -4295,25 +4194,25 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B53" s="2">
-        <v>0.4339511692523956</v>
+        <v>0.4528201520442963</v>
       </c>
       <c r="C53" s="1">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E53" s="1">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -4321,19 +4220,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B54" s="2">
-        <v>0.4302736222743988</v>
+        <v>0.4528201520442963</v>
       </c>
       <c r="C54" s="1">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -4347,13 +4246,13 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B55" s="2">
-        <v>0.4045307338237763</v>
+        <v>0.4195245504379273</v>
       </c>
       <c r="C55" s="1">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
@@ -4362,7 +4261,7 @@
         <v>220</v>
       </c>
       <c r="F55" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
@@ -4373,19 +4272,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B56" s="2">
-        <v>0.4045307338237763</v>
+        <v>0.4195245504379273</v>
       </c>
       <c r="C56" s="1">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="D56" s="1">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E56" s="1">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -4394,27 +4293,27 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B57" s="2">
-        <v>0.4045307338237763</v>
+        <v>0.3895584940910339</v>
       </c>
       <c r="C57" s="1">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="F57" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
@@ -4425,19 +4324,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B58" s="2">
-        <v>0.3751103281974793</v>
+        <v>0.3795698285102844</v>
       </c>
       <c r="C58" s="1">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -4451,19 +4350,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="B59" s="2">
-        <v>0.3456899225711823</v>
+        <v>0.3695811331272125</v>
       </c>
       <c r="C59" s="1">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D59" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -4472,24 +4371,24 @@
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B60" s="2">
-        <v>0.3273021578788757</v>
+        <v>0.3662515878677368</v>
       </c>
       <c r="C60" s="1">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -4503,19 +4402,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="B61" s="2">
-        <v>0.3236245810985565</v>
+        <v>0.3662515878677368</v>
       </c>
       <c r="C61" s="1">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="D61" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="1">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -4524,27 +4423,27 @@
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B62" s="2">
-        <v>0.3236245810985565</v>
+        <v>0.3662515878677368</v>
       </c>
       <c r="C62" s="1">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F62" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -4555,19 +4454,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="B63" s="2">
-        <v>0.2942041754722595</v>
+        <v>0.3396151065826416</v>
       </c>
       <c r="C63" s="1">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="D63" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -4576,24 +4475,24 @@
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B64" s="2">
-        <v>0.2905266284942627</v>
+        <v>0.3129786252975464</v>
       </c>
       <c r="C64" s="1">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -4607,19 +4506,19 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="B65" s="2">
-        <v>0.283171534538269</v>
+        <v>0.3129786252975464</v>
       </c>
       <c r="C65" s="1">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="D65" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E65" s="1">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -4628,24 +4527,24 @@
         <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B66" s="2">
-        <v>0.2794939577579498</v>
+        <v>0.3096490502357483</v>
       </c>
       <c r="C66" s="1">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -4659,19 +4558,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B67" s="2">
-        <v>0.2647837698459625</v>
+        <v>0.293001264333725</v>
       </c>
       <c r="C67" s="1">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -4685,22 +4584,22 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B68" s="2">
-        <v>0.2611061930656433</v>
+        <v>0.293001264333725</v>
       </c>
       <c r="C68" s="1">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="F68" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -4711,19 +4610,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="B69" s="2">
-        <v>0.2574286460876465</v>
+        <v>0.2663647830486298</v>
       </c>
       <c r="C69" s="1">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E69" s="1">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -4732,24 +4631,24 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B70" s="2">
-        <v>0.2537510991096497</v>
+        <v>0.2630352377891541</v>
       </c>
       <c r="C70" s="1">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -4763,19 +4662,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B71" s="2">
-        <v>0.2537510991096497</v>
+        <v>0.2563761174678803</v>
       </c>
       <c r="C71" s="1">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -4789,19 +4688,19 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="B72" s="2">
-        <v>0.2500735521316528</v>
+        <v>0.2530465424060822</v>
       </c>
       <c r="C72" s="1">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D72" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -4810,24 +4709,24 @@
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B73" s="2">
-        <v>0.242718443274498</v>
+        <v>0.2463874220848084</v>
       </c>
       <c r="C73" s="1">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -4841,22 +4740,22 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B74" s="2">
-        <v>0.2224919050931931</v>
+        <v>0.2397283017635346</v>
       </c>
       <c r="C74" s="1">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="F74" s="1">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
@@ -4867,22 +4766,22 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B75" s="2">
-        <v>0.2206531316041946</v>
+        <v>0.2380635291337967</v>
       </c>
       <c r="C75" s="1">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F75" s="1">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
@@ -4893,48 +4792,48 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B76" s="2">
-        <v>0.2206531316041946</v>
+        <v>0.2363987416028976</v>
       </c>
       <c r="C76" s="1">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="D76" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F76" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B77" s="2">
-        <v>0.209620475769043</v>
+        <v>0.2297396212816238</v>
       </c>
       <c r="C77" s="1">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="F77" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
@@ -4945,45 +4844,45 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="B78" s="2">
-        <v>0.209620475769043</v>
+        <v>0.2264100760221481</v>
       </c>
       <c r="C78" s="1">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="D78" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E78" s="1">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="F78" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="B79" s="2">
-        <v>0.2059429287910461</v>
+        <v>0.1997735947370529</v>
       </c>
       <c r="C79" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D79" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E79" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -4992,27 +4891,27 @@
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B80" s="2">
-        <v>0.1912327110767365</v>
+        <v>0.1897849142551422</v>
       </c>
       <c r="C80" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="F80" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
@@ -5023,19 +4922,19 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B81" s="2">
-        <v>0.1838776171207428</v>
+        <v>0.1864553540945053</v>
       </c>
       <c r="C81" s="1">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -5049,19 +4948,19 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B82" s="2">
-        <v>0.176522508263588</v>
+        <v>0.1831257939338684</v>
       </c>
       <c r="C82" s="1">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="F82" s="1">
         <v>0</v>
@@ -5075,19 +4974,19 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B83" s="2">
-        <v>0.176522508263588</v>
+        <v>0.163148432970047</v>
       </c>
       <c r="C83" s="1">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -5101,19 +5000,19 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B84" s="2">
-        <v>0.1728449612855911</v>
+        <v>0.163148432970047</v>
       </c>
       <c r="C84" s="1">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -5127,19 +5026,19 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B85" s="2">
-        <v>0.1544571965932846</v>
+        <v>0.1598188728094101</v>
       </c>
       <c r="C85" s="1">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -5153,10 +5052,10 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B86" s="2">
-        <v>0.1544571965932846</v>
+        <v>0.1398415118455887</v>
       </c>
       <c r="C86" s="1">
         <v>84</v>
@@ -5179,25 +5078,25 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="B87" s="2">
-        <v>0.1544571965932846</v>
+        <v>0.1398415118455887</v>
       </c>
       <c r="C87" s="1">
         <v>84</v>
       </c>
       <c r="D87" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F87" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G87" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -5205,25 +5104,25 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="B88" s="2">
-        <v>0.1507796347141266</v>
+        <v>0.1398415118455887</v>
       </c>
       <c r="C88" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D88" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E88" s="1">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F88" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -5231,19 +5130,19 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B89" s="2">
-        <v>0.1471020877361298</v>
+        <v>0.1365119516849518</v>
       </c>
       <c r="C89" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5257,19 +5156,19 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B90" s="2">
-        <v>0.1434245407581329</v>
+        <v>0.1265232712030411</v>
       </c>
       <c r="C90" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5283,19 +5182,19 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="B91" s="2">
-        <v>0.1434245407581329</v>
+        <v>0.1265232712030411</v>
       </c>
       <c r="C91" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D91" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E91" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5304,30 +5203,30 @@
         <v>0</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="B92" s="2">
-        <v>0.1397469788789749</v>
+        <v>0.1165345907211304</v>
       </c>
       <c r="C92" s="1">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D92" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E92" s="1">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -5335,19 +5234,19 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B93" s="2">
-        <v>0.1397469788789749</v>
+        <v>0.09988679736852646</v>
       </c>
       <c r="C93" s="1">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5361,19 +5260,19 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="B94" s="2">
-        <v>0.1397469788789749</v>
+        <v>0.09988679736852646</v>
       </c>
       <c r="C94" s="1">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D94" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -5382,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -5390,16 +5289,16 @@
         <v>98</v>
       </c>
       <c r="B95" s="2">
-        <v>0.1360694319009781</v>
+        <v>0.08989811688661575</v>
       </c>
       <c r="C95" s="1">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -5416,16 +5315,16 @@
         <v>99</v>
       </c>
       <c r="B96" s="2">
-        <v>0.1323918849229813</v>
+        <v>0.08656855672597885</v>
       </c>
       <c r="C96" s="1">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -5442,16 +5341,16 @@
         <v>100</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1287143230438232</v>
+        <v>0.07990943640470505</v>
       </c>
       <c r="C97" s="1">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5465,25 +5364,25 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1287143230438232</v>
+        <v>0.07990943640470505</v>
       </c>
       <c r="C98" s="1">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="D98" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
       </c>
       <c r="G98" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
@@ -5491,19 +5390,19 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B99" s="2">
-        <v>0.121359221637249</v>
+        <v>0.07990943640470505</v>
       </c>
       <c r="C99" s="1">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -5517,19 +5416,19 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1140041202306747</v>
+        <v>0.07325031608343124</v>
       </c>
       <c r="C100" s="1">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -5543,25 +5442,25 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1103265658020973</v>
+        <v>0.07325031608343124</v>
       </c>
       <c r="C101" s="1">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D101" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E101" s="1">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F101" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -5572,16 +5471,16 @@
         <v>104</v>
       </c>
       <c r="B102" s="2">
-        <v>0.09929390996694565</v>
+        <v>0.06992075592279434</v>
       </c>
       <c r="C102" s="1">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -5598,16 +5497,16 @@
         <v>105</v>
       </c>
       <c r="B103" s="2">
-        <v>0.09561635553836823</v>
+        <v>0.06326163560152054</v>
       </c>
       <c r="C103" s="1">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -5624,16 +5523,16 @@
         <v>106</v>
       </c>
       <c r="B104" s="2">
-        <v>0.09561635553836823</v>
+        <v>0.06326163560152054</v>
       </c>
       <c r="C104" s="1">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -5650,16 +5549,16 @@
         <v>107</v>
       </c>
       <c r="B105" s="2">
-        <v>0.09561635553836823</v>
+        <v>0.05993207544088364</v>
       </c>
       <c r="C105" s="1">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -5676,16 +5575,16 @@
         <v>108</v>
       </c>
       <c r="B106" s="2">
-        <v>0.09561635553836823</v>
+        <v>0.05993207544088364</v>
       </c>
       <c r="C106" s="1">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -5702,16 +5601,16 @@
         <v>109</v>
       </c>
       <c r="B107" s="2">
-        <v>0.0919388085603714</v>
+        <v>0.05993207544088364</v>
       </c>
       <c r="C107" s="1">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -5728,16 +5627,16 @@
         <v>110</v>
       </c>
       <c r="B108" s="2">
-        <v>0.08826125413179398</v>
+        <v>0.05993207544088364</v>
       </c>
       <c r="C108" s="1">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -5754,16 +5653,16 @@
         <v>111</v>
       </c>
       <c r="B109" s="2">
-        <v>0.08826125413179398</v>
+        <v>0.05327295884490013</v>
       </c>
       <c r="C109" s="1">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -5780,16 +5679,16 @@
         <v>112</v>
       </c>
       <c r="B110" s="2">
-        <v>0.08090614527463913</v>
+        <v>0.05327295884490013</v>
       </c>
       <c r="C110" s="1">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -5803,25 +5702,25 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="B111" s="2">
-        <v>0.08090614527463913</v>
+        <v>0.05327295884490013</v>
       </c>
       <c r="C111" s="1">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D111" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F111" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -5829,19 +5728,19 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B112" s="2">
-        <v>0.0772285982966423</v>
+        <v>0.04994339868426323</v>
       </c>
       <c r="C112" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -5855,19 +5754,19 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B113" s="2">
-        <v>0.06987348943948746</v>
+        <v>0.04994339868426323</v>
       </c>
       <c r="C113" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -5881,19 +5780,19 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B114" s="2">
-        <v>0.06987348943948746</v>
+        <v>0.04661383852362633</v>
       </c>
       <c r="C114" s="1">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -5907,19 +5806,19 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B115" s="2">
-        <v>0.06619594246149063</v>
+        <v>0.04661383852362633</v>
       </c>
       <c r="C115" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -5933,19 +5832,19 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B116" s="2">
-        <v>0.05884083732962608</v>
+        <v>0.03995471820235252</v>
       </c>
       <c r="C116" s="1">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -5959,25 +5858,25 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="B117" s="2">
-        <v>0.05884083732962608</v>
+        <v>0.02663647942245007</v>
       </c>
       <c r="C117" s="1">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D117" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E117" s="1">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -5985,25 +5884,25 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="B118" s="2">
-        <v>0.05148573219776154</v>
+        <v>0.01331823971122503</v>
       </c>
       <c r="C118" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D118" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E118" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -6011,19 +5910,19 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B119" s="2">
-        <v>0.05148573219776154</v>
+        <v>0.01331823971122503</v>
       </c>
       <c r="C119" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
       </c>
       <c r="E119" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -6037,19 +5936,19 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B120" s="2">
-        <v>0.05148573219776154</v>
+        <v>0.01331823971122503</v>
       </c>
       <c r="C120" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -6063,25 +5962,25 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="B121" s="2">
-        <v>0.05148573219776154</v>
+        <v>0.006659119855612516</v>
       </c>
       <c r="C121" s="1">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D121" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E121" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -6089,19 +5988,19 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B122" s="2">
-        <v>0.04780817776918411</v>
+        <v>0.006659119855612516</v>
       </c>
       <c r="C122" s="1">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D122" s="1">
         <v>0</v>
       </c>
       <c r="E122" s="1">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -6115,813 +6014,59 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2">
+        <v>0.006659119855612516</v>
+      </c>
+      <c r="C123" s="1">
+        <v>4</v>
+      </c>
+      <c r="D123" s="1">
+        <v>0</v>
+      </c>
+      <c r="E123" s="1">
+        <v>4</v>
+      </c>
+      <c r="F123" s="1">
+        <v>0</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
         <v>124</v>
       </c>
-      <c r="B123" s="2">
-        <v>0.04413062706589699</v>
-      </c>
-      <c r="C123" s="1">
-        <v>24</v>
-      </c>
-      <c r="D123" s="1">
-        <v>0</v>
-      </c>
-      <c r="E123" s="1">
-        <v>24</v>
-      </c>
-      <c r="F123" s="1">
-        <v>0</v>
-      </c>
-      <c r="G123" s="1">
-        <v>0</v>
-      </c>
-      <c r="H123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B124" s="2">
-        <v>0.04045307263731957</v>
-      </c>
-      <c r="C124" s="1">
-        <v>22</v>
-      </c>
-      <c r="D124" s="1">
-        <v>0</v>
-      </c>
-      <c r="E124" s="1">
-        <v>22</v>
-      </c>
-      <c r="F124" s="1">
-        <v>0</v>
-      </c>
-      <c r="G124" s="1">
-        <v>0</v>
-      </c>
-      <c r="H124" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B125" s="2">
-        <v>0.03309797123074532</v>
-      </c>
-      <c r="C125" s="1">
-        <v>18</v>
-      </c>
-      <c r="D125" s="1">
-        <v>0</v>
-      </c>
-      <c r="E125" s="1">
-        <v>18</v>
-      </c>
-      <c r="F125" s="1">
-        <v>0</v>
-      </c>
-      <c r="G125" s="1">
-        <v>0</v>
-      </c>
-      <c r="H125" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B126" s="2">
-        <v>0.03309797123074532</v>
-      </c>
-      <c r="C126" s="1">
-        <v>18</v>
-      </c>
-      <c r="D126" s="1">
-        <v>0</v>
-      </c>
-      <c r="E126" s="1">
-        <v>18</v>
-      </c>
-      <c r="F126" s="1">
-        <v>0</v>
-      </c>
-      <c r="G126" s="1">
-        <v>0</v>
-      </c>
-      <c r="H126" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B127" s="2">
-        <v>0.02574286609888077</v>
-      </c>
-      <c r="C127" s="1">
-        <v>14</v>
-      </c>
-      <c r="D127" s="1">
-        <v>0</v>
-      </c>
-      <c r="E127" s="1">
-        <v>14</v>
-      </c>
-      <c r="F127" s="1">
-        <v>0</v>
-      </c>
-      <c r="G127" s="1">
-        <v>0</v>
-      </c>
-      <c r="H127" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B128" s="2">
-        <v>0.02574286609888077</v>
-      </c>
-      <c r="C128" s="1">
-        <v>14</v>
-      </c>
-      <c r="D128" s="1">
-        <v>0</v>
-      </c>
-      <c r="E128" s="1">
-        <v>14</v>
-      </c>
-      <c r="F128" s="1">
-        <v>0</v>
-      </c>
-      <c r="G128" s="1">
-        <v>0</v>
-      </c>
-      <c r="H128" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
-      <c r="A129" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B129" s="2">
-        <v>0.02574286609888077</v>
-      </c>
-      <c r="C129" s="1">
-        <v>14</v>
-      </c>
-      <c r="D129" s="1">
-        <v>0</v>
-      </c>
-      <c r="E129" s="1">
-        <v>14</v>
-      </c>
-      <c r="F129" s="1">
-        <v>0</v>
-      </c>
-      <c r="G129" s="1">
-        <v>0</v>
-      </c>
-      <c r="H129" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
-      <c r="A130" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B130" s="2">
-        <v>0.02574286609888077</v>
-      </c>
-      <c r="C130" s="1">
-        <v>14</v>
-      </c>
-      <c r="D130" s="1">
-        <v>0</v>
-      </c>
-      <c r="E130" s="1">
-        <v>14</v>
-      </c>
-      <c r="F130" s="1">
-        <v>0</v>
-      </c>
-      <c r="G130" s="1">
-        <v>0</v>
-      </c>
-      <c r="H130" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
-      <c r="A131" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B131" s="2">
-        <v>0.02206531353294849</v>
-      </c>
-      <c r="C131" s="1">
-        <v>12</v>
-      </c>
-      <c r="D131" s="1">
-        <v>0</v>
-      </c>
-      <c r="E131" s="1">
-        <v>12</v>
-      </c>
-      <c r="F131" s="1">
-        <v>0</v>
-      </c>
-      <c r="G131" s="1">
-        <v>0</v>
-      </c>
-      <c r="H131" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
-      <c r="A132" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B132" s="2">
-        <v>0.02206531353294849</v>
-      </c>
-      <c r="C132" s="1">
-        <v>12</v>
-      </c>
-      <c r="D132" s="1">
-        <v>264</v>
-      </c>
-      <c r="E132" s="1">
-        <v>0</v>
-      </c>
-      <c r="F132" s="1">
-        <v>0</v>
-      </c>
-      <c r="G132" s="1">
-        <v>12</v>
-      </c>
-      <c r="H132" s="1">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B133" s="2">
-        <v>0.02206531353294849</v>
-      </c>
-      <c r="C133" s="1">
-        <v>12</v>
-      </c>
-      <c r="D133" s="1">
-        <v>0</v>
-      </c>
-      <c r="E133" s="1">
-        <v>12</v>
-      </c>
-      <c r="F133" s="1">
-        <v>0</v>
-      </c>
-      <c r="G133" s="1">
-        <v>0</v>
-      </c>
-      <c r="H133" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
-      <c r="A134" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B134" s="2">
-        <v>0.01838776096701622</v>
-      </c>
-      <c r="C134" s="1">
-        <v>10</v>
-      </c>
-      <c r="D134" s="1">
-        <v>0</v>
-      </c>
-      <c r="E134" s="1">
-        <v>10</v>
-      </c>
-      <c r="F134" s="1">
-        <v>0</v>
-      </c>
-      <c r="G134" s="1">
-        <v>0</v>
-      </c>
-      <c r="H134" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
-      <c r="A135" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B135" s="2">
-        <v>0.01838776096701622</v>
-      </c>
-      <c r="C135" s="1">
-        <v>10</v>
-      </c>
-      <c r="D135" s="1">
-        <v>0</v>
-      </c>
-      <c r="E135" s="1">
-        <v>10</v>
-      </c>
-      <c r="F135" s="1">
-        <v>0</v>
-      </c>
-      <c r="G135" s="1">
-        <v>0</v>
-      </c>
-      <c r="H135" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B136" s="2">
-        <v>0.01838776096701622</v>
-      </c>
-      <c r="C136" s="1">
-        <v>10</v>
-      </c>
-      <c r="D136" s="1">
-        <v>0</v>
-      </c>
-      <c r="E136" s="1">
-        <v>10</v>
-      </c>
-      <c r="F136" s="1">
-        <v>0</v>
-      </c>
-      <c r="G136" s="1">
-        <v>0</v>
-      </c>
-      <c r="H136" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
-      <c r="A137" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B137" s="2">
-        <v>0.01471020933240652</v>
-      </c>
-      <c r="C137" s="1">
-        <v>8</v>
-      </c>
-      <c r="D137" s="1">
-        <v>0</v>
-      </c>
-      <c r="E137" s="1">
-        <v>8</v>
-      </c>
-      <c r="F137" s="1">
-        <v>0</v>
-      </c>
-      <c r="G137" s="1">
-        <v>0</v>
-      </c>
-      <c r="H137" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
-      <c r="A138" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B138" s="2">
-        <v>0.01471020933240652</v>
-      </c>
-      <c r="C138" s="1">
-        <v>8</v>
-      </c>
-      <c r="D138" s="1">
-        <v>96</v>
-      </c>
-      <c r="E138" s="1">
-        <v>8</v>
-      </c>
-      <c r="F138" s="1">
-        <v>0</v>
-      </c>
-      <c r="G138" s="1">
-        <v>0</v>
-      </c>
-      <c r="H138" s="1">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
-      <c r="A139" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2">
-        <v>0.01471020933240652</v>
-      </c>
-      <c r="C139" s="1">
-        <v>8</v>
-      </c>
-      <c r="D139" s="1">
-        <v>0</v>
-      </c>
-      <c r="E139" s="1">
-        <v>8</v>
-      </c>
-      <c r="F139" s="1">
-        <v>0</v>
-      </c>
-      <c r="G139" s="1">
-        <v>0</v>
-      </c>
-      <c r="H139" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
-      <c r="A140" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2">
-        <v>0.01471020933240652</v>
-      </c>
-      <c r="C140" s="1">
-        <v>8</v>
-      </c>
-      <c r="D140" s="1">
-        <v>0</v>
-      </c>
-      <c r="E140" s="1">
-        <v>8</v>
-      </c>
-      <c r="F140" s="1">
-        <v>0</v>
-      </c>
-      <c r="G140" s="1">
-        <v>0</v>
-      </c>
-      <c r="H140" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B141" s="2">
-        <v>0.01103265676647425</v>
-      </c>
-      <c r="C141" s="1">
-        <v>6</v>
-      </c>
-      <c r="D141" s="1">
-        <v>0</v>
-      </c>
-      <c r="E141" s="1">
-        <v>6</v>
-      </c>
-      <c r="F141" s="1">
-        <v>0</v>
-      </c>
-      <c r="G141" s="1">
-        <v>0</v>
-      </c>
-      <c r="H141" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
-      <c r="A142" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B142" s="2">
-        <v>0.01103265676647425</v>
-      </c>
-      <c r="C142" s="1">
-        <v>6</v>
-      </c>
-      <c r="D142" s="1">
-        <v>0</v>
-      </c>
-      <c r="E142" s="1">
-        <v>6</v>
-      </c>
-      <c r="F142" s="1">
-        <v>0</v>
-      </c>
-      <c r="G142" s="1">
-        <v>0</v>
-      </c>
-      <c r="H142" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
-      <c r="A143" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B143" s="2">
-        <v>0.01103265676647425</v>
-      </c>
-      <c r="C143" s="1">
-        <v>6</v>
-      </c>
-      <c r="D143" s="1">
-        <v>0</v>
-      </c>
-      <c r="E143" s="1">
-        <v>6</v>
-      </c>
-      <c r="F143" s="1">
-        <v>0</v>
-      </c>
-      <c r="G143" s="1">
-        <v>0</v>
-      </c>
-      <c r="H143" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
-      <c r="A144" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B144" s="2">
-        <v>0.01103265676647425</v>
-      </c>
-      <c r="C144" s="1">
-        <v>6</v>
-      </c>
-      <c r="D144" s="1">
-        <v>0</v>
-      </c>
-      <c r="E144" s="1">
-        <v>6</v>
-      </c>
-      <c r="F144" s="1">
-        <v>0</v>
-      </c>
-      <c r="G144" s="1">
-        <v>0</v>
-      </c>
-      <c r="H144" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B145" s="2">
-        <v>0.01103265676647425</v>
-      </c>
-      <c r="C145" s="1">
-        <v>6</v>
-      </c>
-      <c r="D145" s="1">
-        <v>0</v>
-      </c>
-      <c r="E145" s="1">
-        <v>6</v>
-      </c>
-      <c r="F145" s="1">
-        <v>0</v>
-      </c>
-      <c r="G145" s="1">
-        <v>0</v>
-      </c>
-      <c r="H145" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
-      <c r="A146" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B146" s="2">
-        <v>0.00735510466620326</v>
-      </c>
-      <c r="C146" s="1">
-        <v>4</v>
-      </c>
-      <c r="D146" s="1">
-        <v>0</v>
-      </c>
-      <c r="E146" s="1">
-        <v>4</v>
-      </c>
-      <c r="F146" s="1">
-        <v>0</v>
-      </c>
-      <c r="G146" s="1">
-        <v>0</v>
-      </c>
-      <c r="H146" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
-      <c r="A147" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B147" s="2">
-        <v>0.00735510466620326</v>
-      </c>
-      <c r="C147" s="1">
-        <v>4</v>
-      </c>
-      <c r="D147" s="1">
-        <v>0</v>
-      </c>
-      <c r="E147" s="1">
-        <v>4</v>
-      </c>
-      <c r="F147" s="1">
-        <v>0</v>
-      </c>
-      <c r="G147" s="1">
-        <v>0</v>
-      </c>
-      <c r="H147" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
-      <c r="A148" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B148" s="2">
-        <v>0.00367755233310163</v>
-      </c>
-      <c r="C148" s="1">
-        <v>2</v>
-      </c>
-      <c r="D148" s="1">
-        <v>0</v>
-      </c>
-      <c r="E148" s="1">
-        <v>2</v>
-      </c>
-      <c r="F148" s="1">
-        <v>0</v>
-      </c>
-      <c r="G148" s="1">
-        <v>0</v>
-      </c>
-      <c r="H148" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
-      <c r="A149" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B149" s="2">
-        <v>0.00367755233310163</v>
-      </c>
-      <c r="C149" s="1">
-        <v>2</v>
-      </c>
-      <c r="D149" s="1">
-        <v>0</v>
-      </c>
-      <c r="E149" s="1">
-        <v>2</v>
-      </c>
-      <c r="F149" s="1">
-        <v>0</v>
-      </c>
-      <c r="G149" s="1">
-        <v>0</v>
-      </c>
-      <c r="H149" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B150" s="2">
-        <v>0.00367755233310163</v>
-      </c>
-      <c r="C150" s="1">
-        <v>2</v>
-      </c>
-      <c r="D150" s="1">
-        <v>0</v>
-      </c>
-      <c r="E150" s="1">
-        <v>2</v>
-      </c>
-      <c r="F150" s="1">
-        <v>0</v>
-      </c>
-      <c r="G150" s="1">
-        <v>0</v>
-      </c>
-      <c r="H150" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
-      <c r="A151" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B151" s="2">
-        <v>0.00367755233310163</v>
-      </c>
-      <c r="C151" s="1">
-        <v>2</v>
-      </c>
-      <c r="D151" s="1">
-        <v>0</v>
-      </c>
-      <c r="E151" s="1">
-        <v>2</v>
-      </c>
-      <c r="F151" s="1">
-        <v>0</v>
-      </c>
-      <c r="G151" s="1">
-        <v>0</v>
-      </c>
-      <c r="H151" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
-      <c r="A152" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B152" s="2">
-        <v>0.00367755233310163</v>
-      </c>
-      <c r="C152" s="1">
-        <v>2</v>
-      </c>
-      <c r="D152" s="1">
-        <v>0</v>
-      </c>
-      <c r="E152" s="1">
-        <v>2</v>
-      </c>
-      <c r="F152" s="1">
-        <v>0</v>
-      </c>
-      <c r="G152" s="1">
-        <v>0</v>
-      </c>
-      <c r="H152" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
-      <c r="A153" t="s">
-        <v>153</v>
-      </c>
-      <c r="B153">
+      <c r="B124">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C153">
+      <c r="C124">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D153">
+      <c r="D124">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E153">
+      <c r="E124">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F153">
+      <c r="F124">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G153">
+      <c r="G124">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H153">
+      <c r="H124">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="134">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -56,6 +56,9 @@
     <t>spi.o</t>
   </si>
   <si>
+    <t>dev_power_monitor.o</t>
+  </si>
+  <si>
     <t>dev_dwt_counter.o</t>
   </si>
   <si>
@@ -212,13 +215,13 @@
     <t>stm32g4xx_hal_uart_ex.o</t>
   </si>
   <si>
+    <t>thread_commun.o</t>
+  </si>
+  <si>
     <t>current_loop.o</t>
   </si>
   <si>
     <t>gpio.o</t>
-  </si>
-  <si>
-    <t>thread_commun.o</t>
   </si>
   <si>
     <t>main.o</t>
@@ -543,63 +546,66 @@
                   <c:v>spi.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>dev_power_monitor.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>mvars.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
                 <c:pt idx="121">
@@ -615,100 +621,103 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="122"/>
                 <c:pt idx="0">
-                  <c:v>65.29313659667969</c:v>
+                  <c:v>64.26055145263672</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.618407249450684</c:v>
+                  <c:v>6.513740062713623</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.538859367370606</c:v>
+                  <c:v>6.435449600219727</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.109299182891846</c:v>
+                  <c:v>6.012682914733887</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.1007080078125</c:v>
+                  <c:v>4.0358567237854</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.813698172569275</c:v>
+                  <c:v>2.740154981613159</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.41595733165741</c:v>
+                  <c:v>1.393564581871033</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3523188829422</c:v>
+                  <c:v>1.330932378768921</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.193222522735596</c:v>
+                  <c:v>1.174352169036865</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.9068490862846375</c:v>
+                  <c:v>0.8925076127052307</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.890939474105835</c:v>
+                  <c:v>0.8768495917320252</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.7954816818237305</c:v>
+                  <c:v>0.782901406288147</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5091082453727722</c:v>
+                  <c:v>0.6263211369514465</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4295600950717926</c:v>
+                  <c:v>0.5010569095611572</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.3977408409118652</c:v>
+                  <c:v>0.422766774892807</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3341023027896881</c:v>
+                  <c:v>0.3914507031440735</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3341023027896881</c:v>
+                  <c:v>0.3288185894489288</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.3022830188274384</c:v>
+                  <c:v>0.3288185894489288</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1590963304042816</c:v>
+                  <c:v>0.2975025475025177</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.09148038923740387</c:v>
+                  <c:v>0.1565802842378616</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.07954816520214081</c:v>
+                  <c:v>0.09003366529941559</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.06363853067159653</c:v>
+                  <c:v>0.07829014211893082</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.04772889986634255</c:v>
+                  <c:v>0.06263211369514465</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.04772889986634255</c:v>
+                  <c:v>0.04697408527135849</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.03181926533579826</c:v>
+                  <c:v>0.04697408527135849</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.03181926533579826</c:v>
+                  <c:v>0.03131605684757233</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.03181926533579826</c:v>
+                  <c:v>0.03131605684757233</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.01590963266789913</c:v>
+                  <c:v>0.03131605684757233</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.01590963266789913</c:v>
+                  <c:v>0.01565802842378616</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.01590963266789913</c:v>
+                  <c:v>0.01565802842378616</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.01590963266789913</c:v>
+                  <c:v>0.01565802842378616</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01590963266789913</c:v>
+                  <c:v>0.01565802842378616</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.01565802842378616</c:v>
                 </c:pt>
                 <c:pt idx="121">
                   <c:v>0</c:v>
@@ -842,43 +851,43 @@
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>multiturn_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>cascade_control.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>dev_half_bridge.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>crc16.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>motor_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>heap_4.o</c:v>
@@ -929,16 +938,16 @@
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
                 <c:pt idx="49">
+                  <c:v>thread_commun.o</c:v>
+                </c:pt>
+                <c:pt idx="50">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>thread_commun.o</c:v>
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>i2c.o</c:v>
@@ -1157,367 +1166,367 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="122"/>
                 <c:pt idx="0">
-                  <c:v>5.55370569229126</c:v>
+                  <c:v>5.5169677734375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.310647964477539</c:v>
+                  <c:v>5.275517463684082</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.924418926239014</c:v>
+                  <c:v>4.891843795776367</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.628087997436523</c:v>
+                  <c:v>4.59747314453125</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.908903360366821</c:v>
+                  <c:v>3.883045673370361</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.692481756210327</c:v>
+                  <c:v>3.668055772781372</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.655856609344482</c:v>
+                  <c:v>3.631672859191895</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.416128396987915</c:v>
+                  <c:v>3.393530368804932</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.163081884384155</c:v>
+                  <c:v>3.142157793045044</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.006592512130737</c:v>
+                  <c:v>2.986703634262085</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.503829002380371</c:v>
+                  <c:v>2.487266063690186</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.327362298965454</c:v>
+                  <c:v>2.31196665763855</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.320703268051148</c:v>
+                  <c:v>2.305351495742798</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.194180011749268</c:v>
+                  <c:v>2.179665327072144</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.147566080093384</c:v>
+                  <c:v>2.133359909057617</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.001065492630005</c:v>
+                  <c:v>1.987828254699707</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.971099376678467</c:v>
+                  <c:v>1.958060503005981</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.794632792472839</c:v>
+                  <c:v>1.782761096954346</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.641473054885864</c:v>
+                  <c:v>1.630614519119263</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.591529607772827</c:v>
+                  <c:v>1.58100152015686</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.385096907615662</c:v>
+                  <c:v>1.461930274963379</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.315176129341126</c:v>
+                  <c:v>1.375934362411499</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.305187463760376</c:v>
+                  <c:v>1.30647611618042</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.258573651313782</c:v>
+                  <c:v>1.296553492546082</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.198641538619995</c:v>
+                  <c:v>1.250248074531555</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.188652873039246</c:v>
+                  <c:v>1.190712451934815</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.165345907211304</c:v>
+                  <c:v>1.180789828300476</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.102084279060364</c:v>
+                  <c:v>1.157637119293213</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.088766098022461</c:v>
+                  <c:v>1.094793915748596</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.065459132194519</c:v>
+                  <c:v>1.081563830375671</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.038822650909424</c:v>
+                  <c:v>1.058411002159119</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.9256176352500916</c:v>
+                  <c:v>1.031950831413269</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.8590264320373535</c:v>
+                  <c:v>0.91949462890625</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.8523673415184021</c:v>
+                  <c:v>0.8467288613319397</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.8457081913948059</c:v>
+                  <c:v>0.8401137590408325</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.7674635648727417</c:v>
+                  <c:v>0.7623867392539978</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.7524805068969727</c:v>
+                  <c:v>0.7475028038024902</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7524805068969727</c:v>
+                  <c:v>0.7475028038024902</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.7358327507972717</c:v>
+                  <c:v>0.7309651374816895</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7325031757354736</c:v>
+                  <c:v>0.7276576161384583</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.6825597882270813</c:v>
+                  <c:v>0.6780445575714111</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.6659119725227356</c:v>
+                  <c:v>0.6615068912506104</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.6192981004714966</c:v>
+                  <c:v>0.6152014136314392</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.6093094348907471</c:v>
+                  <c:v>0.6052788496017456</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.5726842880249023</c:v>
+                  <c:v>0.5688959360122681</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.5560364723205566</c:v>
+                  <c:v>0.5523582696914673</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.5527069568634033</c:v>
+                  <c:v>0.5490507483482361</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.5293999910354614</c:v>
+                  <c:v>0.5258979797363281</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.5127522349357605</c:v>
+                  <c:v>0.5093603134155273</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.4628088176250458</c:v>
+                  <c:v>0.469669908285141</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.4528201520442963</c:v>
+                  <c:v>0.459747314453125</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.4528201520442963</c:v>
+                  <c:v>0.4498246908187866</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.4195245504379273</c:v>
+                  <c:v>0.4498246908187866</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.4195245504379273</c:v>
+                  <c:v>0.4167493581771851</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.3895584940910339</c:v>
+                  <c:v>0.3869815468788147</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.3795698285102844</c:v>
+                  <c:v>0.3770589530467987</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.3695811331272125</c:v>
+                  <c:v>0.3671363294124603</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.3662515878677368</c:v>
+                  <c:v>0.3638288080692291</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.3662515878677368</c:v>
+                  <c:v>0.3638288080692291</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.3662515878677368</c:v>
+                  <c:v>0.3638288080692291</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.3396151065826416</c:v>
+                  <c:v>0.33736851811409</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.3129786252975464</c:v>
+                  <c:v>0.3109082579612732</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.3129786252975464</c:v>
+                  <c:v>0.3109082579612732</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.3096490502357483</c:v>
+                  <c:v>0.3076007068157196</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.293001264333725</c:v>
+                  <c:v>0.2910630404949188</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.293001264333725</c:v>
+                  <c:v>0.2910630404949188</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.2663647830486298</c:v>
+                  <c:v>0.2646027505397797</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.2630352377891541</c:v>
+                  <c:v>0.2612952291965485</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.2563761174678803</c:v>
+                  <c:v>0.2546801567077637</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.2530465424060822</c:v>
+                  <c:v>0.2513726353645325</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.2463874220848084</c:v>
+                  <c:v>0.2447575628757477</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.2397283017635346</c:v>
+                  <c:v>0.2381424903869629</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.2380635291337967</c:v>
+                  <c:v>0.2364887148141861</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.2363987416028976</c:v>
+                  <c:v>0.2348349541425705</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.2297396212816238</c:v>
+                  <c:v>0.2282198816537857</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.2264100760221481</c:v>
+                  <c:v>0.2249123454093933</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.1997735947370529</c:v>
+                  <c:v>0.1984520703554153</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.1897849142551422</c:v>
+                  <c:v>0.1885294765233994</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.1864553540945053</c:v>
+                  <c:v>0.185221940279007</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.1831257939338684</c:v>
+                  <c:v>0.1819144040346146</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.163148432970047</c:v>
+                  <c:v>0.1620691865682602</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.163148432970047</c:v>
+                  <c:v>0.1620691865682602</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.1598188728094101</c:v>
+                  <c:v>0.158761665225029</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.1398415118455887</c:v>
+                  <c:v>0.1389164477586746</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.1398415118455887</c:v>
+                  <c:v>0.1389164477586746</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.1398415118455887</c:v>
+                  <c:v>0.1389164477586746</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.1365119516849518</c:v>
+                  <c:v>0.1356089115142822</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.1265232712030411</c:v>
+                  <c:v>0.1256863176822662</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.1265232712030411</c:v>
+                  <c:v>0.1256863176822662</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.1165345907211304</c:v>
+                  <c:v>0.1157637089490891</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.09988679736852646</c:v>
+                  <c:v>0.09922603517770767</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.09988679736852646</c:v>
+                  <c:v>0.09922603517770767</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.08989811688661575</c:v>
+                  <c:v>0.08930343389511108</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.08656855672597885</c:v>
+                  <c:v>0.08599589765071869</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.07990943640470505</c:v>
+                  <c:v>0.0793808326125145</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.07990943640470505</c:v>
+                  <c:v>0.0793808326125145</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.07990943640470505</c:v>
+                  <c:v>0.0793808326125145</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.07325031608343124</c:v>
+                  <c:v>0.07276576012372971</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.07325031608343124</c:v>
+                  <c:v>0.07276576012372971</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.06992075592279434</c:v>
+                  <c:v>0.06945822387933731</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.06326163560152054</c:v>
+                  <c:v>0.06284315884113312</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.06326163560152054</c:v>
+                  <c:v>0.06284315884113312</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.05993207544088364</c:v>
+                  <c:v>0.05953562259674072</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.05993207544088364</c:v>
+                  <c:v>0.05953562259674072</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.05993207544088364</c:v>
+                  <c:v>0.05953562259674072</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.05993207544088364</c:v>
+                  <c:v>0.05953562259674072</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.05327295884490013</c:v>
+                  <c:v>0.05292055383324623</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.05327295884490013</c:v>
+                  <c:v>0.05292055383324623</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.05327295884490013</c:v>
+                  <c:v>0.05292055383324623</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.04994339868426323</c:v>
+                  <c:v>0.04961301758885384</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.04994339868426323</c:v>
+                  <c:v>0.04961301758885384</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.04661383852362633</c:v>
+                  <c:v>0.04630548506975174</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.04661383852362633</c:v>
+                  <c:v>0.04630548506975174</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.03995471820235252</c:v>
+                  <c:v>0.03969041630625725</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.02663647942245007</c:v>
+                  <c:v>0.02646027691662312</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.01331823971122503</c:v>
+                  <c:v>0.01323013845831156</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.01331823971122503</c:v>
+                  <c:v>0.01323013845831156</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.01331823971122503</c:v>
+                  <c:v>0.01323013845831156</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.006659119855612516</c:v>
+                  <c:v>0.006615069229155779</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.006659119855612516</c:v>
+                  <c:v>0.006615069229155779</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.006659119855612516</c:v>
+                  <c:v>0.006615069229155779</c:v>
                 </c:pt>
                 <c:pt idx="121">
                   <c:v>0</c:v>
@@ -1955,28 +1964,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1984,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>65.29313659667969</v>
+        <v>64.26055145263672</v>
       </c>
       <c r="C3" s="1">
         <v>16416</v>
@@ -2010,16 +2019,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>6.618407249450684</v>
+        <v>6.513740062713623</v>
       </c>
       <c r="C4" s="1">
         <v>1664</v>
       </c>
       <c r="D4" s="1">
-        <v>516</v>
+        <v>884</v>
       </c>
       <c r="E4" s="1">
-        <v>516</v>
+        <v>884</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -2036,7 +2045,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>6.538859367370606</v>
+        <v>6.435449600219727</v>
       </c>
       <c r="C5" s="1">
         <v>1644</v>
@@ -2062,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>6.109299182891846</v>
+        <v>6.012682914733887</v>
       </c>
       <c r="C6" s="1">
         <v>1536</v>
@@ -2088,7 +2097,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.1007080078125</v>
+        <v>4.0358567237854</v>
       </c>
       <c r="C7" s="1">
         <v>1031</v>
@@ -2114,10 +2123,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>1.813698172569275</v>
+        <v>2.740154981613159</v>
       </c>
       <c r="C8" s="1">
-        <v>456</v>
+        <v>700</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -2132,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>456</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2140,7 +2149,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1.41595733165741</v>
+        <v>1.393564581871033</v>
       </c>
       <c r="C9" s="1">
         <v>356</v>
@@ -2166,7 +2175,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>1.3523188829422</v>
+        <v>1.330932378768921</v>
       </c>
       <c r="C10" s="1">
         <v>340</v>
@@ -2192,7 +2201,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.193222522735596</v>
+        <v>1.174352169036865</v>
       </c>
       <c r="C11" s="1">
         <v>300</v>
@@ -2218,7 +2227,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.9068490862846375</v>
+        <v>0.8925076127052307</v>
       </c>
       <c r="C12" s="1">
         <v>228</v>
@@ -2244,7 +2253,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.890939474105835</v>
+        <v>0.8768495917320252</v>
       </c>
       <c r="C13" s="1">
         <v>224</v>
@@ -2270,7 +2279,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.7954816818237305</v>
+        <v>0.782901406288147</v>
       </c>
       <c r="C14" s="1">
         <v>200</v>
@@ -2296,16 +2305,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.5091082453727722</v>
+        <v>0.6263211369514465</v>
       </c>
       <c r="C15" s="1">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="D15" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2314,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>128</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2322,16 +2331,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.4295600950717926</v>
+        <v>0.5010569095611572</v>
       </c>
       <c r="C16" s="1">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="E16" s="1">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2340,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2348,16 +2357,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.3977408409118652</v>
+        <v>0.422766774892807</v>
       </c>
       <c r="C17" s="1">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D17" s="1">
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="E17" s="1">
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2366,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2374,16 +2383,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3341023027896881</v>
+        <v>0.3914507031440735</v>
       </c>
       <c r="C18" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D18" s="1">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="E18" s="1">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2392,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2400,19 +2409,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3341023027896881</v>
+        <v>0.3288185894489288</v>
       </c>
       <c r="C19" s="1">
         <v>84</v>
       </c>
       <c r="D19" s="1">
-        <v>442</v>
+        <v>252</v>
       </c>
       <c r="E19" s="1">
-        <v>386</v>
+        <v>252</v>
       </c>
       <c r="F19" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -2426,25 +2435,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.3022830188274384</v>
+        <v>0.3288185894489288</v>
       </c>
       <c r="C20" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D20" s="1">
-        <v>136</v>
+        <v>442</v>
       </c>
       <c r="E20" s="1">
-        <v>136</v>
+        <v>386</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2452,25 +2461,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.1590963304042816</v>
+        <v>0.2975025475025177</v>
       </c>
       <c r="C21" s="1">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D21" s="1">
+        <v>136</v>
+      </c>
+      <c r="E21" s="1">
+        <v>136</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
         <v>76</v>
-      </c>
-      <c r="E21" s="1">
-        <v>76</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2478,25 +2487,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.09148038923740387</v>
+        <v>0.1565802842378616</v>
       </c>
       <c r="C22" s="1">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D22" s="1">
-        <v>461</v>
+        <v>76</v>
       </c>
       <c r="E22" s="1">
-        <v>426</v>
+        <v>76</v>
       </c>
       <c r="F22" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2504,25 +2513,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.07954816520214081</v>
+        <v>0.09003366529941559</v>
       </c>
       <c r="C23" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D23" s="1">
-        <v>188</v>
+        <v>461</v>
       </c>
       <c r="E23" s="1">
-        <v>188</v>
+        <v>426</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H23" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2530,25 +2539,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.06363853067159653</v>
+        <v>0.07829014211893082</v>
       </c>
       <c r="C24" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D24" s="1">
-        <v>2958</v>
+        <v>188</v>
       </c>
       <c r="E24" s="1">
-        <v>2942</v>
+        <v>188</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2556,22 +2565,22 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.04772889986634255</v>
+        <v>0.06263211369514465</v>
       </c>
       <c r="C25" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D25" s="1">
-        <v>70</v>
+        <v>2958</v>
       </c>
       <c r="E25" s="1">
-        <v>58</v>
+        <v>2942</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -2582,16 +2591,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.04772889986634255</v>
+        <v>0.04697408527135849</v>
       </c>
       <c r="C26" s="1">
         <v>12</v>
       </c>
       <c r="D26" s="1">
-        <v>714</v>
+        <v>70</v>
       </c>
       <c r="E26" s="1">
-        <v>702</v>
+        <v>58</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2608,22 +2617,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.03181926533579826</v>
+        <v>0.04697408527135849</v>
       </c>
       <c r="C27" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D27" s="1">
-        <v>8</v>
+        <v>714</v>
       </c>
       <c r="E27" s="1">
-        <v>0</v>
+        <v>702</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2634,19 +2643,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.03181926533579826</v>
+        <v>0.03131605684757233</v>
       </c>
       <c r="C28" s="1">
         <v>8</v>
       </c>
       <c r="D28" s="1">
-        <v>1202</v>
+        <v>8</v>
       </c>
       <c r="E28" s="1">
-        <v>1014</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
         <v>8</v>
@@ -2660,19 +2669,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.03181926533579826</v>
+        <v>0.03131605684757233</v>
       </c>
       <c r="C29" s="1">
         <v>8</v>
       </c>
       <c r="D29" s="1">
-        <v>1078</v>
+        <v>1202</v>
       </c>
       <c r="E29" s="1">
-        <v>1070</v>
+        <v>1014</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G29" s="1">
         <v>8</v>
@@ -2686,22 +2695,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.01590963266789913</v>
+        <v>0.03131605684757233</v>
       </c>
       <c r="C30" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1">
-        <v>4</v>
+        <v>1078</v>
       </c>
       <c r="E30" s="1">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2712,16 +2721,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.01590963266789913</v>
+        <v>0.01565802842378616</v>
       </c>
       <c r="C31" s="1">
         <v>4</v>
       </c>
       <c r="D31" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E31" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2738,19 +2747,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.01590963266789913</v>
+        <v>0.01565802842378616</v>
       </c>
       <c r="C32" s="1">
         <v>4</v>
       </c>
       <c r="D32" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E32" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
         <v>4</v>
@@ -2764,19 +2773,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.01590963266789913</v>
+        <v>0.01565802842378616</v>
       </c>
       <c r="C33" s="1">
         <v>4</v>
       </c>
       <c r="D33" s="1">
-        <v>272</v>
+        <v>44</v>
       </c>
       <c r="E33" s="1">
-        <v>268</v>
+        <v>16</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G33" s="1">
         <v>4</v>
@@ -2790,19 +2799,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01590963266789913</v>
+        <v>0.01565802842378616</v>
       </c>
       <c r="C34" s="1">
         <v>4</v>
       </c>
       <c r="D34" s="1">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="E34" s="1">
-        <v>48</v>
+        <v>268</v>
       </c>
       <c r="F34" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>4</v>
@@ -2811,9 +2820,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.01565802842378616</v>
+      </c>
+      <c r="C35" s="1">
+        <v>4</v>
+      </c>
+      <c r="D35" s="1">
+        <v>84</v>
+      </c>
+      <c r="E35" s="1">
+        <v>48</v>
+      </c>
+      <c r="F35" s="1">
+        <v>32</v>
+      </c>
+      <c r="G35" s="1">
+        <v>4</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B124">
         <f>SUBTOTAL(109,[ram_percent])</f>
@@ -2868,36 +2903,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" t="s">
         <v>132</v>
-      </c>
-      <c r="C2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2">
-        <v>5.55370569229126</v>
+        <v>5.5169677734375</v>
       </c>
       <c r="C3" s="1">
         <v>3336</v>
@@ -2920,10 +2955,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2">
-        <v>5.310647964477539</v>
+        <v>5.275517463684082</v>
       </c>
       <c r="C4" s="1">
         <v>3190</v>
@@ -2946,10 +2981,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2">
-        <v>4.924418926239014</v>
+        <v>4.891843795776367</v>
       </c>
       <c r="C5" s="1">
         <v>2958</v>
@@ -2972,10 +3007,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2">
-        <v>4.628087997436523</v>
+        <v>4.59747314453125</v>
       </c>
       <c r="C6" s="1">
         <v>2780</v>
@@ -2998,10 +3033,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2">
-        <v>3.908903360366821</v>
+        <v>3.883045673370361</v>
       </c>
       <c r="C7" s="1">
         <v>2348</v>
@@ -3024,10 +3059,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2">
-        <v>3.692481756210327</v>
+        <v>3.668055772781372</v>
       </c>
       <c r="C8" s="1">
         <v>2218</v>
@@ -3050,10 +3085,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2">
-        <v>3.655856609344482</v>
+        <v>3.631672859191895</v>
       </c>
       <c r="C9" s="1">
         <v>2196</v>
@@ -3076,10 +3111,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2">
-        <v>3.416128396987915</v>
+        <v>3.393530368804932</v>
       </c>
       <c r="C10" s="1">
         <v>2052</v>
@@ -3102,10 +3137,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2">
-        <v>3.163081884384155</v>
+        <v>3.142157793045044</v>
       </c>
       <c r="C11" s="1">
         <v>1900</v>
@@ -3128,10 +3163,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2">
-        <v>3.006592512130737</v>
+        <v>2.986703634262085</v>
       </c>
       <c r="C12" s="1">
         <v>1806</v>
@@ -3157,7 +3192,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="2">
-        <v>2.503829002380371</v>
+        <v>2.487266063690186</v>
       </c>
       <c r="C13" s="1">
         <v>1504</v>
@@ -3180,10 +3215,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2">
-        <v>2.327362298965454</v>
+        <v>2.31196665763855</v>
       </c>
       <c r="C14" s="1">
         <v>1398</v>
@@ -3206,10 +3241,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2">
-        <v>2.320703268051148</v>
+        <v>2.305351495742798</v>
       </c>
       <c r="C15" s="1">
         <v>1394</v>
@@ -3232,10 +3267,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2">
-        <v>2.194180011749268</v>
+        <v>2.179665327072144</v>
       </c>
       <c r="C16" s="1">
         <v>1318</v>
@@ -3258,10 +3293,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="2">
-        <v>2.147566080093384</v>
+        <v>2.133359909057617</v>
       </c>
       <c r="C17" s="1">
         <v>1290</v>
@@ -3284,10 +3319,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>2.001065492630005</v>
+        <v>1.987828254699707</v>
       </c>
       <c r="C18" s="1">
         <v>1202</v>
@@ -3310,10 +3345,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2">
-        <v>1.971099376678467</v>
+        <v>1.958060503005981</v>
       </c>
       <c r="C19" s="1">
         <v>1184</v>
@@ -3336,10 +3371,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2">
-        <v>1.794632792472839</v>
+        <v>1.782761096954346</v>
       </c>
       <c r="C20" s="1">
         <v>1078</v>
@@ -3362,10 +3397,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2">
-        <v>1.641473054885864</v>
+        <v>1.630614519119263</v>
       </c>
       <c r="C21" s="1">
         <v>986</v>
@@ -3388,10 +3423,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2">
-        <v>1.591529607772827</v>
+        <v>1.58100152015686</v>
       </c>
       <c r="C22" s="1">
         <v>956</v>
@@ -3414,19 +3449,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B23" s="2">
-        <v>1.385096907615662</v>
+        <v>1.461930274963379</v>
       </c>
       <c r="C23" s="1">
-        <v>832</v>
+        <v>884</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>1664</v>
       </c>
       <c r="E23" s="1">
-        <v>832</v>
+        <v>884</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -3435,76 +3470,76 @@
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2">
-        <v>1.315176129341126</v>
+        <v>1.375934362411499</v>
       </c>
       <c r="C24" s="1">
-        <v>790</v>
+        <v>832</v>
       </c>
       <c r="D24" s="1">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>434</v>
+        <v>832</v>
       </c>
       <c r="F24" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2">
-        <v>1.305187463760376</v>
+        <v>1.30647611618042</v>
       </c>
       <c r="C25" s="1">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E25" s="1">
-        <v>784</v>
+        <v>434</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2">
-        <v>1.258573651313782</v>
+        <v>1.296553492546082</v>
       </c>
       <c r="C26" s="1">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="D26" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -3513,24 +3548,24 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B27" s="2">
-        <v>1.198641538619995</v>
+        <v>1.250248074531555</v>
       </c>
       <c r="C27" s="1">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E27" s="1">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -3539,30 +3574,30 @@
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B28" s="2">
-        <v>1.188652873039246</v>
+        <v>1.190712451934815</v>
       </c>
       <c r="C28" s="1">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="D28" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>702</v>
+        <v>720</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -3570,25 +3605,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1.165345907211304</v>
+        <v>1.180789828300476</v>
       </c>
       <c r="C29" s="1">
-        <v>700</v>
+        <v>714</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -3599,16 +3634,16 @@
         <v>53</v>
       </c>
       <c r="B30" s="2">
-        <v>1.102084279060364</v>
+        <v>1.157637119293213</v>
       </c>
       <c r="C30" s="1">
-        <v>662</v>
+        <v>700</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>662</v>
+        <v>700</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -3625,19 +3660,19 @@
         <v>54</v>
       </c>
       <c r="B31" s="2">
-        <v>1.088766098022461</v>
+        <v>1.094793915748596</v>
       </c>
       <c r="C31" s="1">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>318</v>
+        <v>662</v>
       </c>
       <c r="F31" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -3648,54 +3683,54 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="B32" s="2">
-        <v>1.065459132194519</v>
+        <v>1.081563830375671</v>
       </c>
       <c r="C32" s="1">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="D32" s="1">
-        <v>1644</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>636</v>
+        <v>318</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G32" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>1640</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="B33" s="2">
-        <v>1.038822650909424</v>
+        <v>1.058411002159119</v>
       </c>
       <c r="C33" s="1">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>1644</v>
       </c>
       <c r="E33" s="1">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3703,19 +3738,19 @@
         <v>56</v>
       </c>
       <c r="B34" s="2">
-        <v>0.9256176352500916</v>
+        <v>1.031950831413269</v>
       </c>
       <c r="C34" s="1">
-        <v>556</v>
+        <v>624</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>44</v>
+        <v>624</v>
       </c>
       <c r="F34" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -3726,28 +3761,28 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="B35" s="2">
-        <v>0.8590264320373535</v>
+        <v>0.91949462890625</v>
       </c>
       <c r="C35" s="1">
-        <v>516</v>
+        <v>556</v>
       </c>
       <c r="D35" s="1">
-        <v>1664</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>516</v>
+        <v>44</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>1664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3755,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>0.8523673415184021</v>
+        <v>0.8467288613319397</v>
       </c>
       <c r="C36" s="1">
         <v>512</v>
@@ -3781,7 +3816,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>0.8457081913948059</v>
+        <v>0.8401137590408325</v>
       </c>
       <c r="C37" s="1">
         <v>508</v>
@@ -3804,10 +3839,10 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38" s="2">
-        <v>0.7674635648727417</v>
+        <v>0.7623867392539978</v>
       </c>
       <c r="C38" s="1">
         <v>461</v>
@@ -3830,10 +3865,10 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B39" s="2">
-        <v>0.7524805068969727</v>
+        <v>0.7475028038024902</v>
       </c>
       <c r="C39" s="1">
         <v>452</v>
@@ -3859,7 +3894,7 @@
         <v>5</v>
       </c>
       <c r="B40" s="2">
-        <v>0.7524805068969727</v>
+        <v>0.7475028038024902</v>
       </c>
       <c r="C40" s="1">
         <v>452</v>
@@ -3882,10 +3917,10 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B41" s="2">
-        <v>0.7358327507972717</v>
+        <v>0.7309651374816895</v>
       </c>
       <c r="C41" s="1">
         <v>442</v>
@@ -3908,10 +3943,10 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7325031757354736</v>
+        <v>0.7276576161384583</v>
       </c>
       <c r="C42" s="1">
         <v>440</v>
@@ -3934,10 +3969,10 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43" s="2">
-        <v>0.6825597882270813</v>
+        <v>0.6780445575714111</v>
       </c>
       <c r="C43" s="1">
         <v>410</v>
@@ -3960,10 +3995,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B44" s="2">
-        <v>0.6659119725227356</v>
+        <v>0.6615068912506104</v>
       </c>
       <c r="C44" s="1">
         <v>400</v>
@@ -3986,10 +4021,10 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B45" s="2">
-        <v>0.6192981004714966</v>
+        <v>0.6152014136314392</v>
       </c>
       <c r="C45" s="1">
         <v>372</v>
@@ -4012,10 +4047,10 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B46" s="2">
-        <v>0.6093094348907471</v>
+        <v>0.6052788496017456</v>
       </c>
       <c r="C46" s="1">
         <v>366</v>
@@ -4041,7 +4076,7 @@
         <v>8</v>
       </c>
       <c r="B47" s="2">
-        <v>0.5726842880249023</v>
+        <v>0.5688959360122681</v>
       </c>
       <c r="C47" s="1">
         <v>344</v>
@@ -4064,10 +4099,10 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B48" s="2">
-        <v>0.5560364723205566</v>
+        <v>0.5523582696914673</v>
       </c>
       <c r="C48" s="1">
         <v>334</v>
@@ -4093,7 +4128,7 @@
         <v>12</v>
       </c>
       <c r="B49" s="2">
-        <v>0.5527069568634033</v>
+        <v>0.5490507483482361</v>
       </c>
       <c r="C49" s="1">
         <v>332</v>
@@ -4116,10 +4151,10 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B50" s="2">
-        <v>0.5293999910354614</v>
+        <v>0.5258979797363281</v>
       </c>
       <c r="C50" s="1">
         <v>318</v>
@@ -4142,10 +4177,10 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B51" s="2">
-        <v>0.5127522349357605</v>
+        <v>0.5093603134155273</v>
       </c>
       <c r="C51" s="1">
         <v>308</v>
@@ -4168,22 +4203,22 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B52" s="2">
-        <v>0.4628088176250458</v>
+        <v>0.469669908285141</v>
       </c>
       <c r="C52" s="1">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F52" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
@@ -4194,25 +4229,25 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B53" s="2">
-        <v>0.4528201520442963</v>
+        <v>0.459747314453125</v>
       </c>
       <c r="C53" s="1">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -4220,25 +4255,25 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B54" s="2">
-        <v>0.4528201520442963</v>
+        <v>0.4498246908187866</v>
       </c>
       <c r="C54" s="1">
         <v>272</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E54" s="1">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -4246,22 +4281,22 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B55" s="2">
-        <v>0.4195245504379273</v>
+        <v>0.4498246908187866</v>
       </c>
       <c r="C55" s="1">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="F55" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
@@ -4272,10 +4307,10 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B56" s="2">
-        <v>0.4195245504379273</v>
+        <v>0.4167493581771851</v>
       </c>
       <c r="C56" s="1">
         <v>252</v>
@@ -4298,10 +4333,10 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B57" s="2">
-        <v>0.3895584940910339</v>
+        <v>0.3869815468788147</v>
       </c>
       <c r="C57" s="1">
         <v>234</v>
@@ -4324,10 +4359,10 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B58" s="2">
-        <v>0.3795698285102844</v>
+        <v>0.3770589530467987</v>
       </c>
       <c r="C58" s="1">
         <v>228</v>
@@ -4350,10 +4385,10 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B59" s="2">
-        <v>0.3695811331272125</v>
+        <v>0.3671363294124603</v>
       </c>
       <c r="C59" s="1">
         <v>222</v>
@@ -4376,10 +4411,10 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B60" s="2">
-        <v>0.3662515878677368</v>
+        <v>0.3638288080692291</v>
       </c>
       <c r="C60" s="1">
         <v>220</v>
@@ -4402,10 +4437,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B61" s="2">
-        <v>0.3662515878677368</v>
+        <v>0.3638288080692291</v>
       </c>
       <c r="C61" s="1">
         <v>220</v>
@@ -4428,10 +4463,10 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B62" s="2">
-        <v>0.3662515878677368</v>
+        <v>0.3638288080692291</v>
       </c>
       <c r="C62" s="1">
         <v>220</v>
@@ -4454,10 +4489,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B63" s="2">
-        <v>0.3396151065826416</v>
+        <v>0.33736851811409</v>
       </c>
       <c r="C63" s="1">
         <v>204</v>
@@ -4480,10 +4515,10 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B64" s="2">
-        <v>0.3129786252975464</v>
+        <v>0.3109082579612732</v>
       </c>
       <c r="C64" s="1">
         <v>188</v>
@@ -4506,10 +4541,10 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B65" s="2">
-        <v>0.3129786252975464</v>
+        <v>0.3109082579612732</v>
       </c>
       <c r="C65" s="1">
         <v>188</v>
@@ -4532,10 +4567,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B66" s="2">
-        <v>0.3096490502357483</v>
+        <v>0.3076007068157196</v>
       </c>
       <c r="C66" s="1">
         <v>186</v>
@@ -4558,10 +4593,10 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B67" s="2">
-        <v>0.293001264333725</v>
+        <v>0.2910630404949188</v>
       </c>
       <c r="C67" s="1">
         <v>176</v>
@@ -4584,10 +4619,10 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B68" s="2">
-        <v>0.293001264333725</v>
+        <v>0.2910630404949188</v>
       </c>
       <c r="C68" s="1">
         <v>176</v>
@@ -4613,7 +4648,7 @@
         <v>11</v>
       </c>
       <c r="B69" s="2">
-        <v>0.2663647830486298</v>
+        <v>0.2646027505397797</v>
       </c>
       <c r="C69" s="1">
         <v>160</v>
@@ -4636,10 +4671,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B70" s="2">
-        <v>0.2630352377891541</v>
+        <v>0.2612952291965485</v>
       </c>
       <c r="C70" s="1">
         <v>158</v>
@@ -4662,10 +4697,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B71" s="2">
-        <v>0.2563761174678803</v>
+        <v>0.2546801567077637</v>
       </c>
       <c r="C71" s="1">
         <v>154</v>
@@ -4688,10 +4723,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B72" s="2">
-        <v>0.2530465424060822</v>
+        <v>0.2513726353645325</v>
       </c>
       <c r="C72" s="1">
         <v>152</v>
@@ -4714,10 +4749,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B73" s="2">
-        <v>0.2463874220848084</v>
+        <v>0.2447575628757477</v>
       </c>
       <c r="C73" s="1">
         <v>148</v>
@@ -4740,10 +4775,10 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B74" s="2">
-        <v>0.2397283017635346</v>
+        <v>0.2381424903869629</v>
       </c>
       <c r="C74" s="1">
         <v>144</v>
@@ -4766,10 +4801,10 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B75" s="2">
-        <v>0.2380635291337967</v>
+        <v>0.2364887148141861</v>
       </c>
       <c r="C75" s="1">
         <v>143</v>
@@ -4792,10 +4827,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B76" s="2">
-        <v>0.2363987416028976</v>
+        <v>0.2348349541425705</v>
       </c>
       <c r="C76" s="1">
         <v>142</v>
@@ -4818,10 +4853,10 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B77" s="2">
-        <v>0.2297396212816238</v>
+        <v>0.2282198816537857</v>
       </c>
       <c r="C77" s="1">
         <v>138</v>
@@ -4844,10 +4879,10 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B78" s="2">
-        <v>0.2264100760221481</v>
+        <v>0.2249123454093933</v>
       </c>
       <c r="C78" s="1">
         <v>136</v>
@@ -4870,10 +4905,10 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B79" s="2">
-        <v>0.1997735947370529</v>
+        <v>0.1984520703554153</v>
       </c>
       <c r="C79" s="1">
         <v>120</v>
@@ -4896,10 +4931,10 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B80" s="2">
-        <v>0.1897849142551422</v>
+        <v>0.1885294765233994</v>
       </c>
       <c r="C80" s="1">
         <v>114</v>
@@ -4922,10 +4957,10 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B81" s="2">
-        <v>0.1864553540945053</v>
+        <v>0.185221940279007</v>
       </c>
       <c r="C81" s="1">
         <v>112</v>
@@ -4948,10 +4983,10 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82" s="2">
-        <v>0.1831257939338684</v>
+        <v>0.1819144040346146</v>
       </c>
       <c r="C82" s="1">
         <v>110</v>
@@ -4974,10 +5009,10 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B83" s="2">
-        <v>0.163148432970047</v>
+        <v>0.1620691865682602</v>
       </c>
       <c r="C83" s="1">
         <v>98</v>
@@ -5000,10 +5035,10 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B84" s="2">
-        <v>0.163148432970047</v>
+        <v>0.1620691865682602</v>
       </c>
       <c r="C84" s="1">
         <v>98</v>
@@ -5026,10 +5061,10 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B85" s="2">
-        <v>0.1598188728094101</v>
+        <v>0.158761665225029</v>
       </c>
       <c r="C85" s="1">
         <v>96</v>
@@ -5052,10 +5087,10 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B86" s="2">
-        <v>0.1398415118455887</v>
+        <v>0.1389164477586746</v>
       </c>
       <c r="C86" s="1">
         <v>84</v>
@@ -5078,10 +5113,10 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B87" s="2">
-        <v>0.1398415118455887</v>
+        <v>0.1389164477586746</v>
       </c>
       <c r="C87" s="1">
         <v>84</v>
@@ -5104,10 +5139,10 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B88" s="2">
-        <v>0.1398415118455887</v>
+        <v>0.1389164477586746</v>
       </c>
       <c r="C88" s="1">
         <v>84</v>
@@ -5130,10 +5165,10 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B89" s="2">
-        <v>0.1365119516849518</v>
+        <v>0.1356089115142822</v>
       </c>
       <c r="C89" s="1">
         <v>82</v>
@@ -5156,10 +5191,10 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B90" s="2">
-        <v>0.1265232712030411</v>
+        <v>0.1256863176822662</v>
       </c>
       <c r="C90" s="1">
         <v>76</v>
@@ -5182,10 +5217,10 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B91" s="2">
-        <v>0.1265232712030411</v>
+        <v>0.1256863176822662</v>
       </c>
       <c r="C91" s="1">
         <v>76</v>
@@ -5208,10 +5243,10 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B92" s="2">
-        <v>0.1165345907211304</v>
+        <v>0.1157637089490891</v>
       </c>
       <c r="C92" s="1">
         <v>70</v>
@@ -5234,10 +5269,10 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B93" s="2">
-        <v>0.09988679736852646</v>
+        <v>0.09922603517770767</v>
       </c>
       <c r="C93" s="1">
         <v>60</v>
@@ -5260,10 +5295,10 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B94" s="2">
-        <v>0.09988679736852646</v>
+        <v>0.09922603517770767</v>
       </c>
       <c r="C94" s="1">
         <v>60</v>
@@ -5286,10 +5321,10 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B95" s="2">
-        <v>0.08989811688661575</v>
+        <v>0.08930343389511108</v>
       </c>
       <c r="C95" s="1">
         <v>54</v>
@@ -5312,10 +5347,10 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B96" s="2">
-        <v>0.08656855672597885</v>
+        <v>0.08599589765071869</v>
       </c>
       <c r="C96" s="1">
         <v>52</v>
@@ -5338,10 +5373,10 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B97" s="2">
-        <v>0.07990943640470505</v>
+        <v>0.0793808326125145</v>
       </c>
       <c r="C97" s="1">
         <v>48</v>
@@ -5364,10 +5399,10 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B98" s="2">
-        <v>0.07990943640470505</v>
+        <v>0.0793808326125145</v>
       </c>
       <c r="C98" s="1">
         <v>48</v>
@@ -5390,10 +5425,10 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B99" s="2">
-        <v>0.07990943640470505</v>
+        <v>0.0793808326125145</v>
       </c>
       <c r="C99" s="1">
         <v>48</v>
@@ -5416,10 +5451,10 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B100" s="2">
-        <v>0.07325031608343124</v>
+        <v>0.07276576012372971</v>
       </c>
       <c r="C100" s="1">
         <v>44</v>
@@ -5442,10 +5477,10 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B101" s="2">
-        <v>0.07325031608343124</v>
+        <v>0.07276576012372971</v>
       </c>
       <c r="C101" s="1">
         <v>44</v>
@@ -5468,10 +5503,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B102" s="2">
-        <v>0.06992075592279434</v>
+        <v>0.06945822387933731</v>
       </c>
       <c r="C102" s="1">
         <v>42</v>
@@ -5494,10 +5529,10 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B103" s="2">
-        <v>0.06326163560152054</v>
+        <v>0.06284315884113312</v>
       </c>
       <c r="C103" s="1">
         <v>38</v>
@@ -5520,10 +5555,10 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B104" s="2">
-        <v>0.06326163560152054</v>
+        <v>0.06284315884113312</v>
       </c>
       <c r="C104" s="1">
         <v>38</v>
@@ -5546,10 +5581,10 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B105" s="2">
-        <v>0.05993207544088364</v>
+        <v>0.05953562259674072</v>
       </c>
       <c r="C105" s="1">
         <v>36</v>
@@ -5572,10 +5607,10 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B106" s="2">
-        <v>0.05993207544088364</v>
+        <v>0.05953562259674072</v>
       </c>
       <c r="C106" s="1">
         <v>36</v>
@@ -5598,10 +5633,10 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B107" s="2">
-        <v>0.05993207544088364</v>
+        <v>0.05953562259674072</v>
       </c>
       <c r="C107" s="1">
         <v>36</v>
@@ -5624,10 +5659,10 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B108" s="2">
-        <v>0.05993207544088364</v>
+        <v>0.05953562259674072</v>
       </c>
       <c r="C108" s="1">
         <v>36</v>
@@ -5650,10 +5685,10 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B109" s="2">
-        <v>0.05327295884490013</v>
+        <v>0.05292055383324623</v>
       </c>
       <c r="C109" s="1">
         <v>32</v>
@@ -5676,10 +5711,10 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B110" s="2">
-        <v>0.05327295884490013</v>
+        <v>0.05292055383324623</v>
       </c>
       <c r="C110" s="1">
         <v>32</v>
@@ -5702,10 +5737,10 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B111" s="2">
-        <v>0.05327295884490013</v>
+        <v>0.05292055383324623</v>
       </c>
       <c r="C111" s="1">
         <v>32</v>
@@ -5728,10 +5763,10 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B112" s="2">
-        <v>0.04994339868426323</v>
+        <v>0.04961301758885384</v>
       </c>
       <c r="C112" s="1">
         <v>30</v>
@@ -5754,10 +5789,10 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B113" s="2">
-        <v>0.04994339868426323</v>
+        <v>0.04961301758885384</v>
       </c>
       <c r="C113" s="1">
         <v>30</v>
@@ -5780,10 +5815,10 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B114" s="2">
-        <v>0.04661383852362633</v>
+        <v>0.04630548506975174</v>
       </c>
       <c r="C114" s="1">
         <v>28</v>
@@ -5806,10 +5841,10 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B115" s="2">
-        <v>0.04661383852362633</v>
+        <v>0.04630548506975174</v>
       </c>
       <c r="C115" s="1">
         <v>28</v>
@@ -5832,10 +5867,10 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B116" s="2">
-        <v>0.03995471820235252</v>
+        <v>0.03969041630625725</v>
       </c>
       <c r="C116" s="1">
         <v>24</v>
@@ -5858,10 +5893,10 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B117" s="2">
-        <v>0.02663647942245007</v>
+        <v>0.02646027691662312</v>
       </c>
       <c r="C117" s="1">
         <v>16</v>
@@ -5884,10 +5919,10 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B118" s="2">
-        <v>0.01331823971122503</v>
+        <v>0.01323013845831156</v>
       </c>
       <c r="C118" s="1">
         <v>8</v>
@@ -5910,10 +5945,10 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B119" s="2">
-        <v>0.01331823971122503</v>
+        <v>0.01323013845831156</v>
       </c>
       <c r="C119" s="1">
         <v>8</v>
@@ -5936,10 +5971,10 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B120" s="2">
-        <v>0.01331823971122503</v>
+        <v>0.01323013845831156</v>
       </c>
       <c r="C120" s="1">
         <v>8</v>
@@ -5962,10 +5997,10 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B121" s="2">
-        <v>0.006659119855612516</v>
+        <v>0.006615069229155779</v>
       </c>
       <c r="C121" s="1">
         <v>4</v>
@@ -5988,10 +6023,10 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B122" s="2">
-        <v>0.006659119855612516</v>
+        <v>0.006615069229155779</v>
       </c>
       <c r="C122" s="1">
         <v>4</v>
@@ -6014,10 +6049,10 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B123" s="2">
-        <v>0.006659119855612516</v>
+        <v>0.006615069229155779</v>
       </c>
       <c r="C123" s="1">
         <v>4</v>
@@ -6040,7 +6075,7 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B124">
         <f>SUBTOTAL(109,[flash_percent])</f>
